--- a/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly EAF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pumped storage" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load shedding" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="System" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Weekly EAF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pumped storage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Load shedding" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,13 +149,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -165,6 +165,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <areaChart>
@@ -178,10 +179,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -206,10 +207,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -234,10 +235,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -262,10 +263,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -290,10 +291,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -318,10 +319,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -346,10 +347,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -374,10 +375,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -402,7 +403,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -423,8 +424,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -434,13 +435,14 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -448,12 +450,13 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -462,7 +465,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -477,9 +480,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1882,7 +1885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1939,7 +1942,7 @@
         <v>46281</v>
       </c>
       <c r="D5" t="n">
-        <v>7276.273208333333</v>
+        <v>7275.770666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1947,7 +1950,7 @@
         <v>46282</v>
       </c>
       <c r="D6" t="n">
-        <v>8198.786833333334</v>
+        <v>8195.647916666667</v>
       </c>
     </row>
     <row r="7">
@@ -1955,7 +1958,7 @@
         <v>46283</v>
       </c>
       <c r="D7" t="n">
-        <v>8080.088499999999</v>
+        <v>8078.570499999999</v>
       </c>
     </row>
     <row r="8">
@@ -1963,7 +1966,7 @@
         <v>46284</v>
       </c>
       <c r="D8" t="n">
-        <v>7455.216125</v>
+        <v>7455.722125</v>
       </c>
     </row>
     <row r="9">
@@ -1971,7 +1974,7 @@
         <v>46285</v>
       </c>
       <c r="D9" t="n">
-        <v>7884.74775</v>
+        <v>7883.662125</v>
       </c>
     </row>
     <row r="10">
@@ -1985,7 +1988,7 @@
         <v>22046.701375</v>
       </c>
       <c r="D10" t="n">
-        <v>8024.222125</v>
+        <v>8025.694458333334</v>
       </c>
     </row>
     <row r="11">
@@ -1999,7 +2002,7 @@
         <v>22009.86975</v>
       </c>
       <c r="D11" t="n">
-        <v>7955.02275</v>
+        <v>7956.46025</v>
       </c>
     </row>
     <row r="12">
@@ -2013,7 +2016,7 @@
         <v>22016.05041666667</v>
       </c>
       <c r="D12" t="n">
-        <v>7125.68</v>
+        <v>7212.929375</v>
       </c>
     </row>
     <row r="13">
@@ -2024,10 +2027,10 @@
         <v>19482.998125</v>
       </c>
       <c r="C13" t="n">
-        <v>20964.82333333333</v>
+        <v>20979.59504166667</v>
       </c>
       <c r="D13" t="n">
-        <v>6833.211708333333</v>
+        <v>6860.059166666667</v>
       </c>
     </row>
     <row r="14">
@@ -2038,10 +2041,10 @@
         <v>19487.81275</v>
       </c>
       <c r="C14" t="n">
-        <v>21270.039625</v>
+        <v>21272.60275</v>
       </c>
       <c r="D14" t="n">
-        <v>7743.892708333333</v>
+        <v>7883.889916666666</v>
       </c>
     </row>
     <row r="15">
@@ -2052,10 +2055,10 @@
         <v>19238.67066666667</v>
       </c>
       <c r="C15" t="n">
-        <v>20775.606875</v>
+        <v>20781.39920833333</v>
       </c>
       <c r="D15" t="n">
-        <v>8756.826500000001</v>
+        <v>9119.132083333332</v>
       </c>
     </row>
     <row r="16">
@@ -2066,10 +2069,38 @@
         <v>17666.642625</v>
       </c>
       <c r="C16" t="n">
-        <v>19897.53754166667</v>
+        <v>19897.02958333333</v>
       </c>
       <c r="D16" t="n">
-        <v>8517.416874999999</v>
+        <v>8885.141250000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B17" t="n">
+        <v>19681.941125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>21513.714875</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6962.981958333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B18" t="n">
+        <v>20481.45475</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22921.01858333333</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7601.899583333333</v>
       </c>
     </row>
   </sheetData>
@@ -2138,16 +2169,16 @@
         <v>46118</v>
       </c>
       <c r="B3" t="n">
-        <v>62.26354655185958</v>
+        <v>62.2635465518596</v>
       </c>
       <c r="C3" t="n">
         <v>16.25394405043937</v>
       </c>
       <c r="D3" t="n">
-        <v>21.28298498634162</v>
+        <v>21.2829849863416</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1995244113594335</v>
+        <v>0.1995244113594334</v>
       </c>
     </row>
     <row r="4">
@@ -2430,7 +2461,7 @@
         <v>71.87410320196696</v>
       </c>
       <c r="C20" t="n">
-        <v>11.8610603915608</v>
+        <v>11.86106039156081</v>
       </c>
       <c r="D20" t="n">
         <v>16.04586943088007</v>
@@ -2569,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2945,6 +2976,38 @@
       </c>
       <c r="J11" t="n">
         <v>71.55025553662692</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B12" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>87.94117647058823</v>
+      </c>
+      <c r="D12" t="n">
+        <v>87.94117647058823</v>
+      </c>
+      <c r="E12" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.77611940298507</v>
+      </c>
+      <c r="G12" t="n">
+        <v>42.77611940298507</v>
+      </c>
+      <c r="H12" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>71.03918228279386</v>
+      </c>
+      <c r="J12" t="n">
+        <v>66.26916524701873</v>
       </c>
     </row>
   </sheetData>
@@ -2958,7 +3021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3126,6 +3189,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
@@ -189,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$14</f>
+              <f>'Chart'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$14</f>
+              <f>'Chart'!$C$2:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$14</f>
+              <f>'Chart'!$D$2:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$14</f>
+              <f>'Chart'!$E$2:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$14</f>
+              <f>'Chart'!$F$2:$F$16</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$14</f>
+              <f>'Chart'!$G$2:$G$16</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$14</f>
+              <f>'Chart'!$H$2:$H$16</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$14</f>
+              <f>'Chart'!$J$2:$J$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$14</f>
+              <f>'Chart'!$I$2:$I$16</f>
             </numRef>
           </val>
         </ser>
@@ -408,10 +408,22 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="30"/>
-        <tickMarkSkip val="30"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -958,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1010,6 +1022,11 @@
           <t>Other</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -1039,6 +1056,11 @@
       <c r="I2" t="n">
         <v>45.88970833333334</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sep/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1309,13 +1331,13 @@
         <v>16906.600875</v>
       </c>
       <c r="C12" t="n">
-        <v>1137.985041666667</v>
+        <v>1137.985916666667</v>
       </c>
       <c r="D12" t="n">
         <v>650.5766666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>597.09075</v>
+        <v>600.653</v>
       </c>
       <c r="F12" t="n">
         <v>600.951</v>
@@ -1327,7 +1349,7 @@
         <v>122.7449583333333</v>
       </c>
       <c r="I12" t="n">
-        <v>47.15108333333333</v>
+        <v>46.15108333333333</v>
       </c>
     </row>
     <row r="13">
@@ -1338,13 +1360,13 @@
         <v>16634.63670833334</v>
       </c>
       <c r="C13" t="n">
-        <v>999.2019583333334</v>
+        <v>999.1999583333333</v>
       </c>
       <c r="D13" t="n">
         <v>651.1357916666667</v>
       </c>
       <c r="E13" t="n">
-        <v>490.8830833333333</v>
+        <v>497.6774166666667</v>
       </c>
       <c r="F13" t="n">
         <v>601.398</v>
@@ -1356,7 +1378,7 @@
         <v>146.1078333333333</v>
       </c>
       <c r="I13" t="n">
-        <v>46.85116666666666</v>
+        <v>45.85116666666666</v>
       </c>
     </row>
     <row r="14">
@@ -1367,13 +1389,13 @@
         <v>15218.227</v>
       </c>
       <c r="C14" t="n">
-        <v>1558.510583333333</v>
+        <v>1569.01675</v>
       </c>
       <c r="D14" t="n">
         <v>651.7128333333334</v>
       </c>
       <c r="E14" t="n">
-        <v>624.9517916666667</v>
+        <v>614.9376666666667</v>
       </c>
       <c r="F14" t="n">
         <v>600.1207083333334</v>
@@ -1385,7 +1407,65 @@
         <v>169.6042916666667</v>
       </c>
       <c r="I14" t="n">
-        <v>47.43254166666667</v>
+        <v>46.43254166666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B15" t="n">
+        <v>17159.56579166666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1067.197791666667</v>
+      </c>
+      <c r="D15" t="n">
+        <v>653.1169583333334</v>
+      </c>
+      <c r="E15" t="n">
+        <v>718.2165833333333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>599.3914166666667</v>
+      </c>
+      <c r="G15" t="n">
+        <v>512.2461666666667</v>
+      </c>
+      <c r="H15" t="n">
+        <v>165.1888333333333</v>
+      </c>
+      <c r="I15" t="n">
+        <v>46.359375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17998.38133333333</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1437.702583333333</v>
+      </c>
+      <c r="D16" t="n">
+        <v>653.9607083333334</v>
+      </c>
+      <c r="E16" t="n">
+        <v>956.6061249999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>601.0589583333333</v>
+      </c>
+      <c r="G16" t="n">
+        <v>390.4469583333334</v>
+      </c>
+      <c r="H16" t="n">
+        <v>180.2736666666667</v>
+      </c>
+      <c r="I16" t="n">
+        <v>45.255125</v>
       </c>
     </row>
   </sheetData>
@@ -1395,6 +1475,1315 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>coal</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>gas</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>hydro</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pumped_storage</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>biomass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2" t="n">
+        <v>17693.9875</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>138.2768333333333</v>
+      </c>
+      <c r="E2" t="n">
+        <v>652.98425</v>
+      </c>
+      <c r="F2" t="n">
+        <v>301.9749166666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>484.1149166666667</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1278.61225</v>
+      </c>
+      <c r="I2" t="n">
+        <v>562.601125</v>
+      </c>
+      <c r="J2" t="n">
+        <v>45.88970833333334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3" t="n">
+        <v>17275.527</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>165.5623333333333</v>
+      </c>
+      <c r="E3" t="n">
+        <v>652.6445416666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>336.6506666666667</v>
+      </c>
+      <c r="G3" t="n">
+        <v>507.22575</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1594.529416666667</v>
+      </c>
+      <c r="I3" t="n">
+        <v>618.0322916666667</v>
+      </c>
+      <c r="J3" t="n">
+        <v>47.15379166666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4" t="n">
+        <v>16370.0085</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>170.00225</v>
+      </c>
+      <c r="E4" t="n">
+        <v>652.5475</v>
+      </c>
+      <c r="F4" t="n">
+        <v>359.9209583333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>428.7385833333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2893.856708333333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>876.8808749999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>46.64266666666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B5" t="n">
+        <v>17449.15991666667</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>153.4750833333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>653.47925</v>
+      </c>
+      <c r="F5" t="n">
+        <v>349.8301666666667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>290.3386666666667</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3069.8105</v>
+      </c>
+      <c r="I5" t="n">
+        <v>367.928125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>47.29916666666667</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B6" t="n">
+        <v>17407.89666666667</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0004166666666666667</v>
+      </c>
+      <c r="D6" t="n">
+        <v>112.4993333333333</v>
+      </c>
+      <c r="E6" t="n">
+        <v>653.6539583333333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>349.788375</v>
+      </c>
+      <c r="G6" t="n">
+        <v>481.446</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1491.586875</v>
+      </c>
+      <c r="I6" t="n">
+        <v>338.3531666666667</v>
+      </c>
+      <c r="J6" t="n">
+        <v>47.23795833333333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B7" t="n">
+        <v>18280.72470833333</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.333333333333333e-05</v>
+      </c>
+      <c r="D7" t="n">
+        <v>152.834875</v>
+      </c>
+      <c r="E7" t="n">
+        <v>653.3170416666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>380.742375</v>
+      </c>
+      <c r="G7" t="n">
+        <v>372.3356666666667</v>
+      </c>
+      <c r="H7" t="n">
+        <v>563.9242916666666</v>
+      </c>
+      <c r="I7" t="n">
+        <v>515.4672916666667</v>
+      </c>
+      <c r="J7" t="n">
+        <v>46.21925</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B8" t="n">
+        <v>18009.53429166667</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.002625</v>
+      </c>
+      <c r="D8" t="n">
+        <v>122.4090416666667</v>
+      </c>
+      <c r="E8" t="n">
+        <v>653.3082083333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>600.8853333333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>422.23925</v>
+      </c>
+      <c r="H8" t="n">
+        <v>687.1719583333334</v>
+      </c>
+      <c r="I8" t="n">
+        <v>781.8878333333333</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46.63491666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B9" t="n">
+        <v>17706.49125</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0007499999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>182.8252916666667</v>
+      </c>
+      <c r="E9" t="n">
+        <v>652.878875</v>
+      </c>
+      <c r="F9" t="n">
+        <v>599.8235000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>375.655375</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1102.776291666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>484.7176666666667</v>
+      </c>
+      <c r="J9" t="n">
+        <v>47.3625</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B10" t="n">
+        <v>17669.532875</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0002916666666666667</v>
+      </c>
+      <c r="D10" t="n">
+        <v>173.9636666666667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>651.9264583333334</v>
+      </c>
+      <c r="F10" t="n">
+        <v>599.5548749999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>447.1493333333333</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1139.28375</v>
+      </c>
+      <c r="I10" t="n">
+        <v>479.9018333333333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47.39183333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B11" t="n">
+        <v>16896.35883333334</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>160.5665416666667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>651.2196250000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>600.0968333333334</v>
+      </c>
+      <c r="G11" t="n">
+        <v>419.5679166666666</v>
+      </c>
+      <c r="H11" t="n">
+        <v>890.0252083333334</v>
+      </c>
+      <c r="I11" t="n">
+        <v>544.627875</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.172125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B12" t="n">
+        <v>16906.600875</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>122.7449583333333</v>
+      </c>
+      <c r="E12" t="n">
+        <v>650.5766666666667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>600.951</v>
+      </c>
+      <c r="G12" t="n">
+        <v>376.0448333333333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1137.985916666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>600.653</v>
+      </c>
+      <c r="J12" t="n">
+        <v>46.15108333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B13" t="n">
+        <v>16634.63670833334</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>146.1078333333333</v>
+      </c>
+      <c r="E13" t="n">
+        <v>651.1357916666667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>601.398</v>
+      </c>
+      <c r="G13" t="n">
+        <v>409.3675</v>
+      </c>
+      <c r="H13" t="n">
+        <v>999.1999583333333</v>
+      </c>
+      <c r="I13" t="n">
+        <v>497.6774166666667</v>
+      </c>
+      <c r="J13" t="n">
+        <v>45.85116666666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15218.227</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>169.6042916666667</v>
+      </c>
+      <c r="E14" t="n">
+        <v>651.7128333333334</v>
+      </c>
+      <c r="F14" t="n">
+        <v>600.1207083333334</v>
+      </c>
+      <c r="G14" t="n">
+        <v>290.2275833333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1569.01675</v>
+      </c>
+      <c r="I14" t="n">
+        <v>614.9376666666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>46.43254166666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B15" t="n">
+        <v>17159.56579166666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>165.1888333333333</v>
+      </c>
+      <c r="E15" t="n">
+        <v>653.1169583333334</v>
+      </c>
+      <c r="F15" t="n">
+        <v>599.3914166666667</v>
+      </c>
+      <c r="G15" t="n">
+        <v>512.2461666666667</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1067.197791666667</v>
+      </c>
+      <c r="I15" t="n">
+        <v>718.2165833333333</v>
+      </c>
+      <c r="J15" t="n">
+        <v>46.359375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17998.38133333333</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>180.2736666666667</v>
+      </c>
+      <c r="E16" t="n">
+        <v>653.9607083333334</v>
+      </c>
+      <c r="F16" t="n">
+        <v>601.0589583333333</v>
+      </c>
+      <c r="G16" t="n">
+        <v>390.4469583333334</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1437.702583333333</v>
+      </c>
+      <c r="I16" t="n">
+        <v>956.6061249999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>45.255125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>residual_demand_mw</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rsa_contracted_demand_mw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unplanned_outages_mw</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46278</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6519.225583333333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6909.73225</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7060.312958333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7275.770666666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8195.647916666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8078.164249999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7415.309041666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7825.248666666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>20545.09083333333</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22046.701375</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8017.758083333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B11" t="n">
+        <v>20375.01329166667</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22009.86975</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7974.924416666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20349.473</v>
+      </c>
+      <c r="C12" t="n">
+        <v>22016.05041666667</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7221.157291666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B13" t="n">
+        <v>19482.998125</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20979.59504166667</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6864.79425</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B14" t="n">
+        <v>19487.81275</v>
+      </c>
+      <c r="C14" t="n">
+        <v>21272.60275</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7876.903208333333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B15" t="n">
+        <v>19238.67066666667</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20781.39920833333</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9102.320750000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17666.642625</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19897.02958333333</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8885.800541666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B17" t="n">
+        <v>19681.941125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>21515.1505</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6962.316666666667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B18" t="n">
+        <v>20481.45475</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22931.62358333333</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7601.149249999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B19" t="n">
+        <v>20850.805125</v>
+      </c>
+      <c r="C19" t="n">
+        <v>23439.71158333333</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8088.340499999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B20" t="n">
+        <v>19957.56466666667</v>
+      </c>
+      <c r="C20" t="n">
+        <v>22034.01633333333</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8612.89925</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>week_start</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>eaf_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>planned_outages_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unplanned_outages_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>other_outages_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2" t="n">
+        <v>63.60801759626349</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.25439581746905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.96564396159935</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1719426246681096</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B3" t="n">
+        <v>62.26354655185958</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16.25394405043937</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.28298498634162</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1995244113594335</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58.14806178711437</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16.83605281195734</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24.93616630455804</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07971909637025129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56.49017237680246</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16.61736210157978</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26.47771084140147</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.414754680216278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B6" t="n">
+        <v>61.48087076801276</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12.9344304746393</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25.5846937966108</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.96073715043171e-06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B7" t="n">
+        <v>61.64690491551136</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13.44849295575325</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24.02505745137972</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8795446773556703</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B8" t="n">
+        <v>66.92968336395393</v>
+      </c>
+      <c r="C8" t="n">
+        <v>13.23125099466557</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19.67176464248445</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.167300998896047</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B9" t="n">
+        <v>68.09581106037895</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.98435294108761</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.91906950169018</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0007664968432588366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B10" t="n">
+        <v>66.68931131118579</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.70358187885527</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20.5959011972248</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0112056127341367</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B11" t="n">
+        <v>65.83665814779673</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12.5776900919222</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.54857459387429</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.03707716640679452</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B12" t="n">
+        <v>64.61325691531795</v>
+      </c>
+      <c r="C12" t="n">
+        <v>13.05439701358587</v>
+      </c>
+      <c r="D12" t="n">
+        <v>21.88952325049659</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4428228205996005</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B13" t="n">
+        <v>68.60639801630951</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.162821755426062</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22.0301226032337</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2006576250307212</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B14" t="n">
+        <v>67.06835662865282</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.838598387785607</v>
+      </c>
+      <c r="D14" t="n">
+        <v>22.93395572957585</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.159089253985713</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B15" t="n">
+        <v>70.1697484679632</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8.744624034041232</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20.98446727726543</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1011602207301399</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B16" t="n">
+        <v>73.85022238959466</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9.982809862247631</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15.86829043932489</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2986773088328317</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75.77742495688942</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.845951345996562</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.362925729455</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01369796765901555</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79.02425364828223</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7.160726322426761</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13.80986953764923</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.005150491641787437</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B19" t="n">
+        <v>77.42775696114812</v>
+      </c>
+      <c r="C19" t="n">
+        <v>10.19960189454833</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12.36861754579994</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00402359850362008</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B20" t="n">
+        <v>71.8740277332906</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11.86106039156081</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.04594489955642</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2189669755921659</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B21" t="n">
+        <v>72.03727613729306</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12.96603419786139</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14.88435741078731</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1123322540582355</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B22" t="n">
+        <v>70.32088085064807</v>
+      </c>
+      <c r="C22" t="n">
+        <v>15.1921513457951</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14.02235076491042</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4646170386464078</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B23" t="n">
+        <v>68.73381666525654</v>
+      </c>
+      <c r="C23" t="n">
+        <v>17.20810517719649</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13.59637793161939</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4617002259275844</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B24" t="n">
+        <v>66.80719641927008</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15.16842524139862</v>
+      </c>
+      <c r="D24" t="n">
+        <v>17.99970163050126</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.02467670883004037</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B25" t="n">
+        <v>69.97910305793802</v>
+      </c>
+      <c r="C25" t="n">
+        <v>13.51588603419731</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.41608615099355</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.08892475687111907</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B26" t="n">
+        <v>71.61789603807085</v>
+      </c>
+      <c r="C26" t="n">
+        <v>12.79330187552352</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.58209362673966</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.006708459665970608</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B27" t="n">
+        <v>69.07928427399533</v>
+      </c>
+      <c r="C27" t="n">
+        <v>14.42079639209718</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.48585926101799</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.01406007288950761</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B28" t="n">
+        <v>72.8913673885815</v>
+      </c>
+      <c r="C28" t="n">
+        <v>12.07345057567374</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14.78732919901175</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2478528367330085</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1414,1206 +2803,6 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>coal</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>gas</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>oil</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>nuclear</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>hydro</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pumped_storage</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>biomass</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B2" t="n">
-        <v>17693.9875</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>138.2768333333333</v>
-      </c>
-      <c r="E2" t="n">
-        <v>652.98425</v>
-      </c>
-      <c r="F2" t="n">
-        <v>301.9749166666667</v>
-      </c>
-      <c r="G2" t="n">
-        <v>484.1149166666667</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1278.61225</v>
-      </c>
-      <c r="I2" t="n">
-        <v>562.601125</v>
-      </c>
-      <c r="J2" t="n">
-        <v>45.88970833333334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B3" t="n">
-        <v>17275.527</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>165.5623333333333</v>
-      </c>
-      <c r="E3" t="n">
-        <v>652.6445416666667</v>
-      </c>
-      <c r="F3" t="n">
-        <v>336.6506666666667</v>
-      </c>
-      <c r="G3" t="n">
-        <v>507.22575</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1594.529416666667</v>
-      </c>
-      <c r="I3" t="n">
-        <v>618.0322916666667</v>
-      </c>
-      <c r="J3" t="n">
-        <v>47.15379166666667</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B4" t="n">
-        <v>16370.0085</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>170.00225</v>
-      </c>
-      <c r="E4" t="n">
-        <v>652.5475</v>
-      </c>
-      <c r="F4" t="n">
-        <v>359.9209583333333</v>
-      </c>
-      <c r="G4" t="n">
-        <v>428.7385833333333</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2893.856708333333</v>
-      </c>
-      <c r="I4" t="n">
-        <v>876.8808749999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>46.64266666666666</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B5" t="n">
-        <v>17449.15991666667</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>153.4750833333333</v>
-      </c>
-      <c r="E5" t="n">
-        <v>653.47925</v>
-      </c>
-      <c r="F5" t="n">
-        <v>349.8301666666667</v>
-      </c>
-      <c r="G5" t="n">
-        <v>290.3386666666667</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3069.8105</v>
-      </c>
-      <c r="I5" t="n">
-        <v>367.928125</v>
-      </c>
-      <c r="J5" t="n">
-        <v>47.29916666666667</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B6" t="n">
-        <v>17407.89666666667</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0004166666666666667</v>
-      </c>
-      <c r="D6" t="n">
-        <v>112.4993333333333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>653.6539583333333</v>
-      </c>
-      <c r="F6" t="n">
-        <v>349.788375</v>
-      </c>
-      <c r="G6" t="n">
-        <v>481.446</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1491.586875</v>
-      </c>
-      <c r="I6" t="n">
-        <v>338.3531666666667</v>
-      </c>
-      <c r="J6" t="n">
-        <v>47.23795833333333</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B7" t="n">
-        <v>18280.72470833333</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8.333333333333333e-05</v>
-      </c>
-      <c r="D7" t="n">
-        <v>152.834875</v>
-      </c>
-      <c r="E7" t="n">
-        <v>653.3170416666667</v>
-      </c>
-      <c r="F7" t="n">
-        <v>380.742375</v>
-      </c>
-      <c r="G7" t="n">
-        <v>372.3356666666667</v>
-      </c>
-      <c r="H7" t="n">
-        <v>563.9242916666666</v>
-      </c>
-      <c r="I7" t="n">
-        <v>515.4672916666667</v>
-      </c>
-      <c r="J7" t="n">
-        <v>46.21925</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B8" t="n">
-        <v>18009.53429166667</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.002625</v>
-      </c>
-      <c r="D8" t="n">
-        <v>122.4090416666667</v>
-      </c>
-      <c r="E8" t="n">
-        <v>653.3082083333334</v>
-      </c>
-      <c r="F8" t="n">
-        <v>600.8853333333333</v>
-      </c>
-      <c r="G8" t="n">
-        <v>422.23925</v>
-      </c>
-      <c r="H8" t="n">
-        <v>687.1719583333334</v>
-      </c>
-      <c r="I8" t="n">
-        <v>781.8878333333333</v>
-      </c>
-      <c r="J8" t="n">
-        <v>46.63491666666667</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B9" t="n">
-        <v>17706.49125</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0007499999999999999</v>
-      </c>
-      <c r="D9" t="n">
-        <v>182.8252916666667</v>
-      </c>
-      <c r="E9" t="n">
-        <v>652.878875</v>
-      </c>
-      <c r="F9" t="n">
-        <v>599.8235000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>375.655375</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1102.776291666667</v>
-      </c>
-      <c r="I9" t="n">
-        <v>484.7176666666667</v>
-      </c>
-      <c r="J9" t="n">
-        <v>47.3625</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B10" t="n">
-        <v>17669.532875</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0002916666666666667</v>
-      </c>
-      <c r="D10" t="n">
-        <v>173.9636666666667</v>
-      </c>
-      <c r="E10" t="n">
-        <v>651.9264583333334</v>
-      </c>
-      <c r="F10" t="n">
-        <v>599.5548749999999</v>
-      </c>
-      <c r="G10" t="n">
-        <v>447.1493333333333</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1139.28375</v>
-      </c>
-      <c r="I10" t="n">
-        <v>479.9018333333333</v>
-      </c>
-      <c r="J10" t="n">
-        <v>47.39183333333333</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B11" t="n">
-        <v>16896.35883333334</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>160.5665416666667</v>
-      </c>
-      <c r="E11" t="n">
-        <v>651.2196250000001</v>
-      </c>
-      <c r="F11" t="n">
-        <v>600.0968333333334</v>
-      </c>
-      <c r="G11" t="n">
-        <v>419.5679166666666</v>
-      </c>
-      <c r="H11" t="n">
-        <v>890.0252083333334</v>
-      </c>
-      <c r="I11" t="n">
-        <v>544.627875</v>
-      </c>
-      <c r="J11" t="n">
-        <v>47.172125</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B12" t="n">
-        <v>16906.600875</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>122.7449583333333</v>
-      </c>
-      <c r="E12" t="n">
-        <v>650.5766666666667</v>
-      </c>
-      <c r="F12" t="n">
-        <v>600.951</v>
-      </c>
-      <c r="G12" t="n">
-        <v>376.0448333333333</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1137.985041666667</v>
-      </c>
-      <c r="I12" t="n">
-        <v>597.09075</v>
-      </c>
-      <c r="J12" t="n">
-        <v>47.15108333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B13" t="n">
-        <v>16634.63670833334</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>146.1078333333333</v>
-      </c>
-      <c r="E13" t="n">
-        <v>651.1357916666667</v>
-      </c>
-      <c r="F13" t="n">
-        <v>601.398</v>
-      </c>
-      <c r="G13" t="n">
-        <v>409.3675</v>
-      </c>
-      <c r="H13" t="n">
-        <v>999.2019583333334</v>
-      </c>
-      <c r="I13" t="n">
-        <v>490.8830833333333</v>
-      </c>
-      <c r="J13" t="n">
-        <v>46.85116666666666</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15218.227</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>169.6042916666667</v>
-      </c>
-      <c r="E14" t="n">
-        <v>651.7128333333334</v>
-      </c>
-      <c r="F14" t="n">
-        <v>600.1207083333334</v>
-      </c>
-      <c r="G14" t="n">
-        <v>290.2275833333333</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1558.510583333333</v>
-      </c>
-      <c r="I14" t="n">
-        <v>624.9517916666667</v>
-      </c>
-      <c r="J14" t="n">
-        <v>47.43254166666667</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>residual_demand_mw</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rsa_contracted_demand_mw</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>unplanned_outages_mw</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46278</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6519.225583333333</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6909.73225</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7060.312958333333</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7275.770666666666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8195.647916666667</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8078.570499999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7455.722125</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7883.662125</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B10" t="n">
-        <v>20545.09083333333</v>
-      </c>
-      <c r="C10" t="n">
-        <v>22046.701375</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8025.694458333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B11" t="n">
-        <v>20375.01329166667</v>
-      </c>
-      <c r="C11" t="n">
-        <v>22009.86975</v>
-      </c>
-      <c r="D11" t="n">
-        <v>7956.46025</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B12" t="n">
-        <v>20349.473</v>
-      </c>
-      <c r="C12" t="n">
-        <v>22016.05041666667</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7212.929375</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B13" t="n">
-        <v>19482.998125</v>
-      </c>
-      <c r="C13" t="n">
-        <v>20979.59504166667</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6860.059166666667</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B14" t="n">
-        <v>19487.81275</v>
-      </c>
-      <c r="C14" t="n">
-        <v>21272.60275</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7883.889916666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B15" t="n">
-        <v>19238.67066666667</v>
-      </c>
-      <c r="C15" t="n">
-        <v>20781.39920833333</v>
-      </c>
-      <c r="D15" t="n">
-        <v>9119.132083333332</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B16" t="n">
-        <v>17666.642625</v>
-      </c>
-      <c r="C16" t="n">
-        <v>19897.02958333333</v>
-      </c>
-      <c r="D16" t="n">
-        <v>8885.141250000001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B17" t="n">
-        <v>19681.941125</v>
-      </c>
-      <c r="C17" t="n">
-        <v>21513.714875</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6962.981958333334</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B18" t="n">
-        <v>20481.45475</v>
-      </c>
-      <c r="C18" t="n">
-        <v>22921.01858333333</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7601.899583333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>week_start</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>eaf_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>planned_outages_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>unplanned_outages_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>other_outages_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B2" t="n">
-        <v>63.60801759626349</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16.25439581746905</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.96564396159935</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.1719426246681096</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46118</v>
-      </c>
-      <c r="B3" t="n">
-        <v>62.2635465518596</v>
-      </c>
-      <c r="C3" t="n">
-        <v>16.25394405043937</v>
-      </c>
-      <c r="D3" t="n">
-        <v>21.2829849863416</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1995244113594334</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46125</v>
-      </c>
-      <c r="B4" t="n">
-        <v>58.14806178711437</v>
-      </c>
-      <c r="C4" t="n">
-        <v>16.83605281195734</v>
-      </c>
-      <c r="D4" t="n">
-        <v>24.93616630455804</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.07971909637025129</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46132</v>
-      </c>
-      <c r="B5" t="n">
-        <v>56.49017237680246</v>
-      </c>
-      <c r="C5" t="n">
-        <v>16.61736210157978</v>
-      </c>
-      <c r="D5" t="n">
-        <v>26.47771084140147</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.414754680216278</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46139</v>
-      </c>
-      <c r="B6" t="n">
-        <v>61.48087076801276</v>
-      </c>
-      <c r="C6" t="n">
-        <v>12.9344304746393</v>
-      </c>
-      <c r="D6" t="n">
-        <v>25.5846937966108</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.96073715043171e-06</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46146</v>
-      </c>
-      <c r="B7" t="n">
-        <v>61.64690491551136</v>
-      </c>
-      <c r="C7" t="n">
-        <v>13.44849295575325</v>
-      </c>
-      <c r="D7" t="n">
-        <v>24.02505745137972</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8795446773556703</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46153</v>
-      </c>
-      <c r="B8" t="n">
-        <v>66.92968336395393</v>
-      </c>
-      <c r="C8" t="n">
-        <v>13.23125099466557</v>
-      </c>
-      <c r="D8" t="n">
-        <v>19.67176464248445</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.167300998896047</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B9" t="n">
-        <v>68.09581106037895</v>
-      </c>
-      <c r="C9" t="n">
-        <v>10.98435294108761</v>
-      </c>
-      <c r="D9" t="n">
-        <v>20.91906950169018</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0007664968432588366</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B10" t="n">
-        <v>66.68931131118579</v>
-      </c>
-      <c r="C10" t="n">
-        <v>12.70358187885527</v>
-      </c>
-      <c r="D10" t="n">
-        <v>20.5959011972248</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0112056127341367</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B11" t="n">
-        <v>65.83665814779673</v>
-      </c>
-      <c r="C11" t="n">
-        <v>12.5776900919222</v>
-      </c>
-      <c r="D11" t="n">
-        <v>21.54857459387429</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.03707716640679452</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B12" t="n">
-        <v>64.61325691531795</v>
-      </c>
-      <c r="C12" t="n">
-        <v>13.05439701358587</v>
-      </c>
-      <c r="D12" t="n">
-        <v>21.88952325049659</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4428228205996005</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B13" t="n">
-        <v>68.60639801630951</v>
-      </c>
-      <c r="C13" t="n">
-        <v>9.162821755426062</v>
-      </c>
-      <c r="D13" t="n">
-        <v>22.0301226032337</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.2006576250307212</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46195</v>
-      </c>
-      <c r="B14" t="n">
-        <v>67.06835662865282</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9.838598387785607</v>
-      </c>
-      <c r="D14" t="n">
-        <v>22.93395572957585</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.159089253985713</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46202</v>
-      </c>
-      <c r="B15" t="n">
-        <v>70.1697484679632</v>
-      </c>
-      <c r="C15" t="n">
-        <v>8.744624034041232</v>
-      </c>
-      <c r="D15" t="n">
-        <v>20.98446727726543</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1011602207301399</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B16" t="n">
-        <v>73.85022238959466</v>
-      </c>
-      <c r="C16" t="n">
-        <v>9.982809862247631</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15.86829043932489</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2986773088328317</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B17" t="n">
-        <v>75.77742495688942</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7.845951345996562</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.362925729455</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.01369796765901555</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79.02425364828223</v>
-      </c>
-      <c r="C18" t="n">
-        <v>7.160726322426761</v>
-      </c>
-      <c r="D18" t="n">
-        <v>13.80986953764923</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.005150491641787437</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B19" t="n">
-        <v>77.42775696114812</v>
-      </c>
-      <c r="C19" t="n">
-        <v>10.19960189454833</v>
-      </c>
-      <c r="D19" t="n">
-        <v>12.36861754579994</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.00402359850362008</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B20" t="n">
-        <v>71.87410320196696</v>
-      </c>
-      <c r="C20" t="n">
-        <v>11.86106039156081</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.04586943088007</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2189669755921659</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B21" t="n">
-        <v>72.03760165733948</v>
-      </c>
-      <c r="C21" t="n">
-        <v>12.96603419786139</v>
-      </c>
-      <c r="D21" t="n">
-        <v>14.88403189074089</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.1123322540582355</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B22" t="n">
-        <v>70.32088085064807</v>
-      </c>
-      <c r="C22" t="n">
-        <v>15.1921513457951</v>
-      </c>
-      <c r="D22" t="n">
-        <v>14.02235076491042</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.4646170386464078</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B23" t="n">
-        <v>68.73381666525654</v>
-      </c>
-      <c r="C23" t="n">
-        <v>17.20810517719649</v>
-      </c>
-      <c r="D23" t="n">
-        <v>13.59637793161939</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4617002259275844</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B24" t="n">
-        <v>66.80349968826333</v>
-      </c>
-      <c r="C24" t="n">
-        <v>15.16842524139862</v>
-      </c>
-      <c r="D24" t="n">
-        <v>18.003398361508</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.02467670883004037</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B25" t="n">
-        <v>69.98297832387561</v>
-      </c>
-      <c r="C25" t="n">
-        <v>13.51588603419731</v>
-      </c>
-      <c r="D25" t="n">
-        <v>16.41221088505596</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.08892475687111907</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B26" t="n">
-        <v>71.61464802350869</v>
-      </c>
-      <c r="C26" t="n">
-        <v>12.79330187552352</v>
-      </c>
-      <c r="D26" t="n">
-        <v>15.58534164130182</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.006708459665970608</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B27" t="n">
-        <v>69.37037239125561</v>
-      </c>
-      <c r="C27" t="n">
-        <v>14.42082404272304</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16.19000255368892</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.01880101233242492</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
           <t>drakensberg_close_unit_hours</t>
         </is>
       </c>
@@ -3008,6 +3197,70 @@
       </c>
       <c r="J12" t="n">
         <v>66.26916524701873</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>84.50980392156863</v>
+      </c>
+      <c r="D13" t="n">
+        <v>84.50980392156863</v>
+      </c>
+      <c r="E13" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.44776119402984</v>
+      </c>
+      <c r="G13" t="n">
+        <v>40.38805970149254</v>
+      </c>
+      <c r="H13" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>68.65417376490629</v>
+      </c>
+      <c r="J13" t="n">
+        <v>68.65417376490629</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83</v>
+      </c>
+      <c r="C14" t="n">
+        <v>81.37254901960785</v>
+      </c>
+      <c r="D14" t="n">
+        <v>80.98039215686272</v>
+      </c>
+      <c r="E14" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="F14" t="n">
+        <v>44.58208955223881</v>
+      </c>
+      <c r="G14" t="n">
+        <v>40.67164179104478</v>
+      </c>
+      <c r="H14" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>59.45485519591141</v>
+      </c>
+      <c r="J14" t="n">
+        <v>59.45485519591141</v>
       </c>
     </row>
   </sheetData>
@@ -3021,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3203,6 +3456,34 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
@@ -160,7 +160,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>South Africa generation mix (Eskom) (to Sep/26)</a:t>
+              <a:t>South Africa generation mix (Eskom) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -189,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$16</f>
+              <f>'Chart'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$16</f>
+              <f>'Chart'!$C$2:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$16</f>
+              <f>'Chart'!$D$2:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$16</f>
+              <f>'Chart'!$E$2:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$16</f>
+              <f>'Chart'!$F$2:$F$18</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$16</f>
+              <f>'Chart'!$G$2:$G$18</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$16</f>
+              <f>'Chart'!$H$2:$H$18</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$16</f>
+              <f>'Chart'!$J$2:$J$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$16</f>
+              <f>'Chart'!$I$2:$I$18</f>
             </numRef>
           </val>
         </ser>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1424,7 +1424,7 @@
         <v>653.1169583333334</v>
       </c>
       <c r="E15" t="n">
-        <v>718.2165833333333</v>
+        <v>719.6522083333333</v>
       </c>
       <c r="F15" t="n">
         <v>599.3914166666667</v>
@@ -1447,13 +1447,13 @@
         <v>17998.38133333333</v>
       </c>
       <c r="C16" t="n">
-        <v>1437.702583333333</v>
+        <v>1438.266041666667</v>
       </c>
       <c r="D16" t="n">
         <v>653.9607083333334</v>
       </c>
       <c r="E16" t="n">
-        <v>956.6061249999999</v>
+        <v>966.6343333333333</v>
       </c>
       <c r="F16" t="n">
         <v>601.0589583333333</v>
@@ -1465,7 +1465,70 @@
         <v>180.2736666666667</v>
       </c>
       <c r="I16" t="n">
-        <v>45.255125</v>
+        <v>45.26845833333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18143.19916666667</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1593.331666666667</v>
+      </c>
+      <c r="D17" t="n">
+        <v>653.6843749999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>951.0985833333334</v>
+      </c>
+      <c r="F17" t="n">
+        <v>602.0205833333333</v>
+      </c>
+      <c r="G17" t="n">
+        <v>554.88675</v>
+      </c>
+      <c r="H17" t="n">
+        <v>196.02275</v>
+      </c>
+      <c r="I17" t="n">
+        <v>44.47620833333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17322.14679166667</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1370.595833333334</v>
+      </c>
+      <c r="D18" t="n">
+        <v>652.6858333333333</v>
+      </c>
+      <c r="E18" t="n">
+        <v>662.9270416666667</v>
+      </c>
+      <c r="F18" t="n">
+        <v>590.4124166666667</v>
+      </c>
+      <c r="G18" t="n">
+        <v>458.823625</v>
+      </c>
+      <c r="H18" t="n">
+        <v>177.8064166666667</v>
+      </c>
+      <c r="I18" t="n">
+        <v>42.92879166666666</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Oct/26</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1480,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1980,7 +2043,7 @@
         <v>1067.197791666667</v>
       </c>
       <c r="I15" t="n">
-        <v>718.2165833333333</v>
+        <v>719.6522083333333</v>
       </c>
       <c r="J15" t="n">
         <v>46.359375</v>
@@ -2009,13 +2072,77 @@
         <v>390.4469583333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1437.702583333333</v>
+        <v>1438.266041666667</v>
       </c>
       <c r="I16" t="n">
-        <v>956.6061249999999</v>
+        <v>966.6343333333333</v>
       </c>
       <c r="J16" t="n">
-        <v>45.255125</v>
+        <v>45.26845833333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18143.19916666667</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>196.02275</v>
+      </c>
+      <c r="E17" t="n">
+        <v>653.6843749999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>602.0205833333333</v>
+      </c>
+      <c r="G17" t="n">
+        <v>554.88675</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1593.331666666667</v>
+      </c>
+      <c r="I17" t="n">
+        <v>951.0985833333334</v>
+      </c>
+      <c r="J17" t="n">
+        <v>44.47620833333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17322.14679166667</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>177.8064166666667</v>
+      </c>
+      <c r="E18" t="n">
+        <v>652.6858333333333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>590.4124166666667</v>
+      </c>
+      <c r="G18" t="n">
+        <v>458.823625</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1370.595833333334</v>
+      </c>
+      <c r="I18" t="n">
+        <v>662.9270416666667</v>
+      </c>
+      <c r="J18" t="n">
+        <v>42.92879166666666</v>
       </c>
     </row>
   </sheetData>
@@ -2664,13 +2791,13 @@
         <v>46251</v>
       </c>
       <c r="B22" t="n">
-        <v>70.32088085064807</v>
+        <v>70.3896680561767</v>
       </c>
       <c r="C22" t="n">
         <v>15.1921513457951</v>
       </c>
       <c r="D22" t="n">
-        <v>14.02235076491042</v>
+        <v>13.95356355938179</v>
       </c>
       <c r="E22" t="n">
         <v>0.4646170386464078</v>
@@ -2698,13 +2825,13 @@
         <v>46265</v>
       </c>
       <c r="B24" t="n">
-        <v>66.80719641927008</v>
+        <v>66.80391652510271</v>
       </c>
       <c r="C24" t="n">
         <v>15.16842524139862</v>
       </c>
       <c r="D24" t="n">
-        <v>17.99970163050126</v>
+        <v>18.00298152466863</v>
       </c>
       <c r="E24" t="n">
         <v>0.02467670883004037</v>
@@ -2715,13 +2842,13 @@
         <v>46272</v>
       </c>
       <c r="B25" t="n">
-        <v>69.97910305793802</v>
+        <v>69.82973700690947</v>
       </c>
       <c r="C25" t="n">
         <v>13.51588603419731</v>
       </c>
       <c r="D25" t="n">
-        <v>16.41608615099355</v>
+        <v>16.5654522020221</v>
       </c>
       <c r="E25" t="n">
         <v>0.08892475687111907</v>
@@ -2732,13 +2859,13 @@
         <v>46279</v>
       </c>
       <c r="B26" t="n">
-        <v>71.61789603807085</v>
+        <v>71.55512250579065</v>
       </c>
       <c r="C26" t="n">
         <v>12.79330187552352</v>
       </c>
       <c r="D26" t="n">
-        <v>15.58209362673966</v>
+        <v>15.64486715901986</v>
       </c>
       <c r="E26" t="n">
         <v>0.006708459665970608</v>
@@ -2749,13 +2876,13 @@
         <v>46286</v>
       </c>
       <c r="B27" t="n">
-        <v>69.07928427399533</v>
+        <v>69.07819471644466</v>
       </c>
       <c r="C27" t="n">
-        <v>14.42079639209718</v>
+        <v>14.42178210618627</v>
       </c>
       <c r="D27" t="n">
-        <v>16.48585926101799</v>
+        <v>16.48596310447957</v>
       </c>
       <c r="E27" t="n">
         <v>0.01406007288950761</v>
@@ -2766,16 +2893,16 @@
         <v>46293</v>
       </c>
       <c r="B28" t="n">
-        <v>72.8913673885815</v>
+        <v>71.27617891822887</v>
       </c>
       <c r="C28" t="n">
-        <v>12.07345057567374</v>
+        <v>12.5866990934773</v>
       </c>
       <c r="D28" t="n">
-        <v>14.78732919901175</v>
+        <v>15.94012167258513</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2478528367330085</v>
+        <v>0.1970003157087015</v>
       </c>
     </row>
   </sheetData>
@@ -2789,7 +2916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3261,6 +3388,38 @@
       </c>
       <c r="J14" t="n">
         <v>59.45485519591141</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>88.52941176470588</v>
+      </c>
+      <c r="D15" t="n">
+        <v>82.15686274509802</v>
+      </c>
+      <c r="E15" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56.55223880597015</v>
+      </c>
+      <c r="G15" t="n">
+        <v>47.58208955223881</v>
+      </c>
+      <c r="H15" t="n">
+        <v>48</v>
+      </c>
+      <c r="I15" t="n">
+        <v>81.7717206132879</v>
+      </c>
+      <c r="J15" t="n">
+        <v>61.49914821124361</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3484,6 +3643,20 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
@@ -189,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$18</f>
+              <f>'Chart'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$18</f>
+              <f>'Chart'!$C$2:$C$21</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$18</f>
+              <f>'Chart'!$D$2:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$18</f>
+              <f>'Chart'!$E$2:$E$21</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$18</f>
+              <f>'Chart'!$F$2:$F$21</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$18</f>
+              <f>'Chart'!$G$2:$G$21</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$18</f>
+              <f>'Chart'!$H$2:$H$21</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +385,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$18</f>
+              <f>'Chart'!$J$2:$J$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$18</f>
+              <f>'Chart'!$I$2:$I$21</f>
             </numRef>
           </val>
         </ser>
@@ -970,7 +970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1447,13 +1447,13 @@
         <v>17998.38133333333</v>
       </c>
       <c r="C16" t="n">
-        <v>1438.266041666667</v>
+        <v>1436.86225</v>
       </c>
       <c r="D16" t="n">
         <v>653.9607083333334</v>
       </c>
       <c r="E16" t="n">
-        <v>966.6343333333333</v>
+        <v>966.917875</v>
       </c>
       <c r="F16" t="n">
         <v>601.0589583333333</v>
@@ -1465,7 +1465,7 @@
         <v>180.2736666666667</v>
       </c>
       <c r="I16" t="n">
-        <v>45.26845833333334</v>
+        <v>45.26491666666666</v>
       </c>
     </row>
     <row r="17">
@@ -1476,13 +1476,13 @@
         <v>18143.19916666667</v>
       </c>
       <c r="C17" t="n">
-        <v>1593.331666666667</v>
+        <v>1593.13</v>
       </c>
       <c r="D17" t="n">
         <v>653.6843749999999</v>
       </c>
       <c r="E17" t="n">
-        <v>951.0985833333334</v>
+        <v>950.426875</v>
       </c>
       <c r="F17" t="n">
         <v>602.0205833333333</v>
@@ -1494,7 +1494,7 @@
         <v>196.02275</v>
       </c>
       <c r="I17" t="n">
-        <v>44.47620833333334</v>
+        <v>44.47370833333333</v>
       </c>
     </row>
     <row r="18">
@@ -1502,10 +1502,10 @@
         <v>46296</v>
       </c>
       <c r="B18" t="n">
-        <v>17322.14679166667</v>
+        <v>17322.27058333333</v>
       </c>
       <c r="C18" t="n">
-        <v>1370.595833333334</v>
+        <v>1375.421666666667</v>
       </c>
       <c r="D18" t="n">
         <v>652.6858333333333</v>
@@ -1517,7 +1517,7 @@
         <v>590.4124166666667</v>
       </c>
       <c r="G18" t="n">
-        <v>458.823625</v>
+        <v>458.717</v>
       </c>
       <c r="H18" t="n">
         <v>177.8064166666667</v>
@@ -1529,6 +1529,93 @@
         <is>
           <t>Oct/26</t>
         </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17702.08925</v>
+      </c>
+      <c r="C19" t="n">
+        <v>811.6795416666668</v>
+      </c>
+      <c r="D19" t="n">
+        <v>652.5819166666666</v>
+      </c>
+      <c r="E19" t="n">
+        <v>581.4985416666667</v>
+      </c>
+      <c r="F19" t="n">
+        <v>602.0305</v>
+      </c>
+      <c r="G19" t="n">
+        <v>437.2321666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>174.4282083333333</v>
+      </c>
+      <c r="I19" t="n">
+        <v>40.59095833333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B20" t="n">
+        <v>16710.90104166667</v>
+      </c>
+      <c r="C20" t="n">
+        <v>760.618875</v>
+      </c>
+      <c r="D20" t="n">
+        <v>651.898</v>
+      </c>
+      <c r="E20" t="n">
+        <v>471.6087083333334</v>
+      </c>
+      <c r="F20" t="n">
+        <v>601.0110833333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>354.256</v>
+      </c>
+      <c r="H20" t="n">
+        <v>163.2662083333333</v>
+      </c>
+      <c r="I20" t="n">
+        <v>39.77541666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B21" t="n">
+        <v>16824.019125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>736.4655833333333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>652.6476666666666</v>
+      </c>
+      <c r="E21" t="n">
+        <v>522.2165</v>
+      </c>
+      <c r="F21" t="n">
+        <v>602.274375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>254.3487916666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>127.8207083333333</v>
+      </c>
+      <c r="I21" t="n">
+        <v>35.279125</v>
       </c>
     </row>
   </sheetData>
@@ -1543,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2072,13 +2159,13 @@
         <v>390.4469583333334</v>
       </c>
       <c r="H16" t="n">
-        <v>1438.266041666667</v>
+        <v>1436.86225</v>
       </c>
       <c r="I16" t="n">
-        <v>966.6343333333333</v>
+        <v>966.917875</v>
       </c>
       <c r="J16" t="n">
-        <v>45.26845833333334</v>
+        <v>45.26491666666666</v>
       </c>
     </row>
     <row r="17">
@@ -2104,13 +2191,13 @@
         <v>554.88675</v>
       </c>
       <c r="H17" t="n">
-        <v>1593.331666666667</v>
+        <v>1593.13</v>
       </c>
       <c r="I17" t="n">
-        <v>951.0985833333334</v>
+        <v>950.426875</v>
       </c>
       <c r="J17" t="n">
-        <v>44.47620833333334</v>
+        <v>44.47370833333333</v>
       </c>
     </row>
     <row r="18">
@@ -2118,7 +2205,7 @@
         <v>46296</v>
       </c>
       <c r="B18" t="n">
-        <v>17322.14679166667</v>
+        <v>17322.27058333333</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -2133,16 +2220,112 @@
         <v>590.4124166666667</v>
       </c>
       <c r="G18" t="n">
-        <v>458.823625</v>
+        <v>458.717</v>
       </c>
       <c r="H18" t="n">
-        <v>1370.595833333334</v>
+        <v>1375.421666666667</v>
       </c>
       <c r="I18" t="n">
         <v>662.9270416666667</v>
       </c>
       <c r="J18" t="n">
         <v>42.92879166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17702.08925</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>174.4282083333333</v>
+      </c>
+      <c r="E19" t="n">
+        <v>652.5819166666666</v>
+      </c>
+      <c r="F19" t="n">
+        <v>602.0305</v>
+      </c>
+      <c r="G19" t="n">
+        <v>437.2321666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>811.6795416666668</v>
+      </c>
+      <c r="I19" t="n">
+        <v>581.4985416666667</v>
+      </c>
+      <c r="J19" t="n">
+        <v>40.59095833333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B20" t="n">
+        <v>16710.90104166667</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>163.2662083333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>651.898</v>
+      </c>
+      <c r="F20" t="n">
+        <v>601.0110833333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>354.256</v>
+      </c>
+      <c r="H20" t="n">
+        <v>760.618875</v>
+      </c>
+      <c r="I20" t="n">
+        <v>471.6087083333334</v>
+      </c>
+      <c r="J20" t="n">
+        <v>39.77541666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B21" t="n">
+        <v>16824.019125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>127.8207083333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>652.6476666666666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>602.274375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>254.3487916666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>736.4655833333333</v>
+      </c>
+      <c r="I21" t="n">
+        <v>522.2165</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.279125</v>
       </c>
     </row>
   </sheetData>
@@ -2156,7 +2339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2273,7 +2456,7 @@
         <v>22009.86975</v>
       </c>
       <c r="D11" t="n">
-        <v>7974.924416666666</v>
+        <v>8146.019416666666</v>
       </c>
     </row>
     <row r="12">
@@ -2287,7 +2470,7 @@
         <v>22016.05041666667</v>
       </c>
       <c r="D12" t="n">
-        <v>7221.157291666666</v>
+        <v>7275.404916666666</v>
       </c>
     </row>
     <row r="13">
@@ -2301,7 +2484,7 @@
         <v>20979.59504166667</v>
       </c>
       <c r="D13" t="n">
-        <v>6864.79425</v>
+        <v>6860.267</v>
       </c>
     </row>
     <row r="14">
@@ -2315,7 +2498,7 @@
         <v>21272.60275</v>
       </c>
       <c r="D14" t="n">
-        <v>7876.903208333333</v>
+        <v>7898.518291666667</v>
       </c>
     </row>
     <row r="15">
@@ -2329,7 +2512,7 @@
         <v>20781.39920833333</v>
       </c>
       <c r="D15" t="n">
-        <v>9102.320750000001</v>
+        <v>9191.260958333332</v>
       </c>
     </row>
     <row r="16">
@@ -2343,7 +2526,7 @@
         <v>19897.02958333333</v>
       </c>
       <c r="D16" t="n">
-        <v>8885.800541666666</v>
+        <v>8952.005333333333</v>
       </c>
     </row>
     <row r="17">
@@ -2357,7 +2540,7 @@
         <v>21515.1505</v>
       </c>
       <c r="D17" t="n">
-        <v>6962.316666666667</v>
+        <v>7141.584416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2371,7 +2554,7 @@
         <v>22931.62358333333</v>
       </c>
       <c r="D18" t="n">
-        <v>7601.149249999999</v>
+        <v>7638.354583333334</v>
       </c>
     </row>
     <row r="19">
@@ -2382,10 +2565,10 @@
         <v>20850.805125</v>
       </c>
       <c r="C19" t="n">
-        <v>23439.71158333333</v>
+        <v>23450.45870833333</v>
       </c>
       <c r="D19" t="n">
-        <v>8088.340499999999</v>
+        <v>8129.333416666667</v>
       </c>
     </row>
     <row r="20">
@@ -2393,13 +2576,69 @@
         <v>46296</v>
       </c>
       <c r="B20" t="n">
-        <v>19957.56466666667</v>
+        <v>19957.53266666667</v>
       </c>
       <c r="C20" t="n">
-        <v>22034.01633333333</v>
+        <v>22001.31016666667</v>
       </c>
       <c r="D20" t="n">
-        <v>8612.89925</v>
+        <v>8604.014458333333</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20358.61125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21754.88029166666</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7610.065291666667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B22" t="n">
+        <v>19307.00045833333</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20541.50345833333</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7244.538124999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B23" t="n">
+        <v>19161.67658333333</v>
+      </c>
+      <c r="C23" t="n">
+        <v>20405.49045833333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8282.062124999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B24" t="n">
+        <v>20288.5225</v>
+      </c>
+      <c r="C24" t="n">
+        <v>21737.09479166667</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8869.295333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2658,7 +2897,7 @@
         <v>67.06835662865282</v>
       </c>
       <c r="C14" t="n">
-        <v>9.838598387785607</v>
+        <v>9.838598387785604</v>
       </c>
       <c r="D14" t="n">
         <v>22.93395572957585</v>
@@ -2825,13 +3064,13 @@
         <v>46265</v>
       </c>
       <c r="B24" t="n">
-        <v>66.80391652510271</v>
+        <v>66.8088601288775</v>
       </c>
       <c r="C24" t="n">
         <v>15.16842524139862</v>
       </c>
       <c r="D24" t="n">
-        <v>18.00298152466863</v>
+        <v>17.99803792089384</v>
       </c>
       <c r="E24" t="n">
         <v>0.02467670883004037</v>
@@ -2842,13 +3081,13 @@
         <v>46272</v>
       </c>
       <c r="B25" t="n">
-        <v>69.82973700690947</v>
+        <v>69.81014911921082</v>
       </c>
       <c r="C25" t="n">
         <v>13.51588603419731</v>
       </c>
       <c r="D25" t="n">
-        <v>16.5654522020221</v>
+        <v>16.58504008972074</v>
       </c>
       <c r="E25" t="n">
         <v>0.08892475687111907</v>
@@ -2859,13 +3098,13 @@
         <v>46279</v>
       </c>
       <c r="B26" t="n">
-        <v>71.55512250579065</v>
+        <v>71.5610659156511</v>
       </c>
       <c r="C26" t="n">
-        <v>12.79330187552352</v>
+        <v>12.79342169490226</v>
       </c>
       <c r="D26" t="n">
-        <v>15.64486715901986</v>
+        <v>15.63880392978068</v>
       </c>
       <c r="E26" t="n">
         <v>0.006708459665970608</v>
@@ -2876,13 +3115,13 @@
         <v>46286</v>
       </c>
       <c r="B27" t="n">
-        <v>69.07819471644466</v>
+        <v>69.08334612635622</v>
       </c>
       <c r="C27" t="n">
         <v>14.42178210618627</v>
       </c>
       <c r="D27" t="n">
-        <v>16.48596310447957</v>
+        <v>16.480811694568</v>
       </c>
       <c r="E27" t="n">
         <v>0.01406007288950761</v>
@@ -2893,16 +3132,16 @@
         <v>46293</v>
       </c>
       <c r="B28" t="n">
-        <v>71.27617891822887</v>
+        <v>71.46892750472888</v>
       </c>
       <c r="C28" t="n">
-        <v>12.5866990934773</v>
+        <v>12.45802183981612</v>
       </c>
       <c r="D28" t="n">
-        <v>15.94012167258513</v>
+        <v>15.82674218605601</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1970003157087015</v>
+        <v>0.2463084693989909</v>
       </c>
     </row>
   </sheetData>
@@ -2916,7 +3155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3420,6 +3659,102 @@
       </c>
       <c r="J15" t="n">
         <v>61.49914821124361</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>89.41176470588236</v>
+      </c>
+      <c r="D16" t="n">
+        <v>88.8235294117647</v>
+      </c>
+      <c r="E16" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45.23880597014925</v>
+      </c>
+      <c r="G16" t="n">
+        <v>45.23880597014925</v>
+      </c>
+      <c r="H16" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>73.76490630323678</v>
+      </c>
+      <c r="J16" t="n">
+        <v>73.76490630323678</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>89.70588235294117</v>
+      </c>
+      <c r="D17" t="n">
+        <v>89.41176470588236</v>
+      </c>
+      <c r="E17" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="F17" t="n">
+        <v>48.14925373134329</v>
+      </c>
+      <c r="G17" t="n">
+        <v>43.82089552238806</v>
+      </c>
+      <c r="H17" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>65.58773424190801</v>
+      </c>
+      <c r="J17" t="n">
+        <v>64.22487223168655</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>87.64705882352942</v>
+      </c>
+      <c r="D18" t="n">
+        <v>87.25490196078431</v>
+      </c>
+      <c r="E18" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35.43283582089552</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34.85074626865672</v>
+      </c>
+      <c r="H18" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>60.81771720613288</v>
+      </c>
+      <c r="J18" t="n">
+        <v>60.81771720613288</v>
       </c>
     </row>
   </sheetData>
@@ -3433,7 +3768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3657,6 +3992,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
@@ -160,6 +160,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>South Africa generation mix (Eskom) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -180,7 +181,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -189,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$21</f>
+              <f>'Chart'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -208,7 +209,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -217,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$21</f>
+              <f>'Chart'!$C$2:$C$24</f>
             </numRef>
           </val>
         </ser>
@@ -236,7 +237,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -245,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$21</f>
+              <f>'Chart'!$D$2:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$21</f>
+              <f>'Chart'!$E$2:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -292,7 +293,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -301,12 +302,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$21</f>
+              <f>'Chart'!$F$2:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -320,7 +321,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -329,12 +330,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$21</f>
+              <f>'Chart'!$G$2:$G$24</f>
             </numRef>
           </val>
         </ser>
@@ -348,7 +349,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -357,12 +358,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$21</f>
+              <f>'Chart'!$H$2:$H$24</f>
             </numRef>
           </val>
         </ser>
@@ -385,12 +386,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$21</f>
+              <f>'Chart'!$J$2:$J$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$21</f>
+              <f>'Chart'!$I$2:$I$24</f>
             </numRef>
           </val>
         </ser>
@@ -970,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1545,7 +1546,7 @@
         <v>652.5819166666666</v>
       </c>
       <c r="E19" t="n">
-        <v>581.4985416666667</v>
+        <v>543.9985416666667</v>
       </c>
       <c r="F19" t="n">
         <v>602.0305</v>
@@ -1574,7 +1575,7 @@
         <v>651.898</v>
       </c>
       <c r="E20" t="n">
-        <v>471.6087083333334</v>
+        <v>434.1087083333334</v>
       </c>
       <c r="F20" t="n">
         <v>601.0110833333333</v>
@@ -1597,13 +1598,13 @@
         <v>16824.019125</v>
       </c>
       <c r="C21" t="n">
-        <v>736.4655833333333</v>
+        <v>742.8995416666667</v>
       </c>
       <c r="D21" t="n">
         <v>652.6476666666666</v>
       </c>
       <c r="E21" t="n">
-        <v>522.2165</v>
+        <v>467.2952083333334</v>
       </c>
       <c r="F21" t="n">
         <v>602.274375</v>
@@ -1616,6 +1617,93 @@
       </c>
       <c r="I21" t="n">
         <v>35.279125</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B22" t="n">
+        <v>17345.563625</v>
+      </c>
+      <c r="C22" t="n">
+        <v>965.618875</v>
+      </c>
+      <c r="D22" t="n">
+        <v>652.3169166666667</v>
+      </c>
+      <c r="E22" t="n">
+        <v>473.020875</v>
+      </c>
+      <c r="F22" t="n">
+        <v>601.4439583333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>607.5314166666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>174.2300833333333</v>
+      </c>
+      <c r="I22" t="n">
+        <v>36.26045833333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B23" t="n">
+        <v>17393.84370833333</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1073.323083333333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>651.74725</v>
+      </c>
+      <c r="E23" t="n">
+        <v>621.4419583333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>601.509875</v>
+      </c>
+      <c r="G23" t="n">
+        <v>479.7298333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>193.3129583333333</v>
+      </c>
+      <c r="I23" t="n">
+        <v>36.0735</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B24" t="n">
+        <v>18107.875375</v>
+      </c>
+      <c r="C24" t="n">
+        <v>431.8802083333333</v>
+      </c>
+      <c r="D24" t="n">
+        <v>652.5202916666667</v>
+      </c>
+      <c r="E24" t="n">
+        <v>552.02</v>
+      </c>
+      <c r="F24" t="n">
+        <v>590.3000416666666</v>
+      </c>
+      <c r="G24" t="n">
+        <v>538.2315</v>
+      </c>
+      <c r="H24" t="n">
+        <v>167.976625</v>
+      </c>
+      <c r="I24" t="n">
+        <v>35.71195833333334</v>
       </c>
     </row>
   </sheetData>
@@ -1625,6 +1713,1672 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>coal</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>gas</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>nuclear</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>hydro</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pumped_storage</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>biomass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2" t="n">
+        <v>17693.9875</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>138.2768333333333</v>
+      </c>
+      <c r="E2" t="n">
+        <v>652.98425</v>
+      </c>
+      <c r="F2" t="n">
+        <v>301.9749166666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>484.1149166666667</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1278.61225</v>
+      </c>
+      <c r="I2" t="n">
+        <v>562.601125</v>
+      </c>
+      <c r="J2" t="n">
+        <v>45.88970833333334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3" t="n">
+        <v>17275.527</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>165.5623333333333</v>
+      </c>
+      <c r="E3" t="n">
+        <v>652.6445416666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>336.6506666666667</v>
+      </c>
+      <c r="G3" t="n">
+        <v>507.22575</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1594.529416666667</v>
+      </c>
+      <c r="I3" t="n">
+        <v>618.0322916666667</v>
+      </c>
+      <c r="J3" t="n">
+        <v>47.15379166666667</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4" t="n">
+        <v>16370.0085</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>170.00225</v>
+      </c>
+      <c r="E4" t="n">
+        <v>652.5475</v>
+      </c>
+      <c r="F4" t="n">
+        <v>359.9209583333333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>428.7385833333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2893.856708333333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>876.8808749999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>46.64266666666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B5" t="n">
+        <v>17449.15991666667</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>153.4750833333333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>653.47925</v>
+      </c>
+      <c r="F5" t="n">
+        <v>349.8301666666667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>290.3386666666667</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3069.8105</v>
+      </c>
+      <c r="I5" t="n">
+        <v>367.928125</v>
+      </c>
+      <c r="J5" t="n">
+        <v>47.29916666666667</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B6" t="n">
+        <v>17407.89666666667</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0004166666666666667</v>
+      </c>
+      <c r="D6" t="n">
+        <v>112.4993333333333</v>
+      </c>
+      <c r="E6" t="n">
+        <v>653.6539583333333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>349.788375</v>
+      </c>
+      <c r="G6" t="n">
+        <v>481.446</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1491.586875</v>
+      </c>
+      <c r="I6" t="n">
+        <v>338.3531666666667</v>
+      </c>
+      <c r="J6" t="n">
+        <v>47.23795833333333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B7" t="n">
+        <v>18280.72470833333</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.333333333333333e-05</v>
+      </c>
+      <c r="D7" t="n">
+        <v>152.834875</v>
+      </c>
+      <c r="E7" t="n">
+        <v>653.3170416666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>380.742375</v>
+      </c>
+      <c r="G7" t="n">
+        <v>372.3356666666667</v>
+      </c>
+      <c r="H7" t="n">
+        <v>563.9242916666666</v>
+      </c>
+      <c r="I7" t="n">
+        <v>515.4672916666667</v>
+      </c>
+      <c r="J7" t="n">
+        <v>46.21925</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B8" t="n">
+        <v>18009.53429166667</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.002625</v>
+      </c>
+      <c r="D8" t="n">
+        <v>122.4090416666667</v>
+      </c>
+      <c r="E8" t="n">
+        <v>653.3082083333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>600.8853333333333</v>
+      </c>
+      <c r="G8" t="n">
+        <v>422.23925</v>
+      </c>
+      <c r="H8" t="n">
+        <v>687.1719583333334</v>
+      </c>
+      <c r="I8" t="n">
+        <v>781.8878333333333</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46.63491666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B9" t="n">
+        <v>17706.49125</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0007499999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>182.8252916666667</v>
+      </c>
+      <c r="E9" t="n">
+        <v>652.878875</v>
+      </c>
+      <c r="F9" t="n">
+        <v>599.8235000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>375.655375</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1102.776291666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>484.7176666666667</v>
+      </c>
+      <c r="J9" t="n">
+        <v>47.3625</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B10" t="n">
+        <v>17669.532875</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0002916666666666667</v>
+      </c>
+      <c r="D10" t="n">
+        <v>173.9636666666667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>651.9264583333334</v>
+      </c>
+      <c r="F10" t="n">
+        <v>599.5548749999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>447.1493333333333</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1139.28375</v>
+      </c>
+      <c r="I10" t="n">
+        <v>479.9018333333333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47.39183333333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B11" t="n">
+        <v>16896.35883333334</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>160.5665416666667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>651.2196250000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>600.0968333333334</v>
+      </c>
+      <c r="G11" t="n">
+        <v>419.5679166666666</v>
+      </c>
+      <c r="H11" t="n">
+        <v>890.0252083333334</v>
+      </c>
+      <c r="I11" t="n">
+        <v>544.627875</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.172125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B12" t="n">
+        <v>16906.600875</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>122.7449583333333</v>
+      </c>
+      <c r="E12" t="n">
+        <v>650.5766666666667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>600.951</v>
+      </c>
+      <c r="G12" t="n">
+        <v>376.0448333333333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1137.985916666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>600.653</v>
+      </c>
+      <c r="J12" t="n">
+        <v>46.15108333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B13" t="n">
+        <v>16634.63670833334</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>146.1078333333333</v>
+      </c>
+      <c r="E13" t="n">
+        <v>651.1357916666667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>601.398</v>
+      </c>
+      <c r="G13" t="n">
+        <v>409.3675</v>
+      </c>
+      <c r="H13" t="n">
+        <v>999.1999583333333</v>
+      </c>
+      <c r="I13" t="n">
+        <v>497.6774166666667</v>
+      </c>
+      <c r="J13" t="n">
+        <v>45.85116666666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>15218.227</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>169.6042916666667</v>
+      </c>
+      <c r="E14" t="n">
+        <v>651.7128333333334</v>
+      </c>
+      <c r="F14" t="n">
+        <v>600.1207083333334</v>
+      </c>
+      <c r="G14" t="n">
+        <v>290.2275833333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1569.01675</v>
+      </c>
+      <c r="I14" t="n">
+        <v>614.9376666666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>46.43254166666667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B15" t="n">
+        <v>17159.56579166666</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>165.1888333333333</v>
+      </c>
+      <c r="E15" t="n">
+        <v>653.1169583333334</v>
+      </c>
+      <c r="F15" t="n">
+        <v>599.3914166666667</v>
+      </c>
+      <c r="G15" t="n">
+        <v>512.2461666666667</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1067.197791666667</v>
+      </c>
+      <c r="I15" t="n">
+        <v>719.6522083333333</v>
+      </c>
+      <c r="J15" t="n">
+        <v>46.359375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17998.38133333333</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>180.2736666666667</v>
+      </c>
+      <c r="E16" t="n">
+        <v>653.9607083333334</v>
+      </c>
+      <c r="F16" t="n">
+        <v>601.0589583333333</v>
+      </c>
+      <c r="G16" t="n">
+        <v>390.4469583333334</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1436.86225</v>
+      </c>
+      <c r="I16" t="n">
+        <v>966.917875</v>
+      </c>
+      <c r="J16" t="n">
+        <v>45.26491666666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18143.19916666667</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>196.02275</v>
+      </c>
+      <c r="E17" t="n">
+        <v>653.6843749999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>602.0205833333333</v>
+      </c>
+      <c r="G17" t="n">
+        <v>554.88675</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1593.13</v>
+      </c>
+      <c r="I17" t="n">
+        <v>950.426875</v>
+      </c>
+      <c r="J17" t="n">
+        <v>44.47370833333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B18" t="n">
+        <v>17322.27058333333</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>177.8064166666667</v>
+      </c>
+      <c r="E18" t="n">
+        <v>652.6858333333333</v>
+      </c>
+      <c r="F18" t="n">
+        <v>590.4124166666667</v>
+      </c>
+      <c r="G18" t="n">
+        <v>458.717</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1375.421666666667</v>
+      </c>
+      <c r="I18" t="n">
+        <v>662.9270416666667</v>
+      </c>
+      <c r="J18" t="n">
+        <v>42.92879166666666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17702.08925</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>174.4282083333333</v>
+      </c>
+      <c r="E19" t="n">
+        <v>652.5819166666666</v>
+      </c>
+      <c r="F19" t="n">
+        <v>602.0305</v>
+      </c>
+      <c r="G19" t="n">
+        <v>437.2321666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>811.6795416666668</v>
+      </c>
+      <c r="I19" t="n">
+        <v>543.9985416666667</v>
+      </c>
+      <c r="J19" t="n">
+        <v>40.59095833333333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B20" t="n">
+        <v>16710.90104166667</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>163.2662083333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>651.898</v>
+      </c>
+      <c r="F20" t="n">
+        <v>601.0110833333333</v>
+      </c>
+      <c r="G20" t="n">
+        <v>354.256</v>
+      </c>
+      <c r="H20" t="n">
+        <v>760.618875</v>
+      </c>
+      <c r="I20" t="n">
+        <v>434.1087083333334</v>
+      </c>
+      <c r="J20" t="n">
+        <v>39.77541666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B21" t="n">
+        <v>16824.019125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>127.8207083333333</v>
+      </c>
+      <c r="E21" t="n">
+        <v>652.6476666666666</v>
+      </c>
+      <c r="F21" t="n">
+        <v>602.274375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>254.3487916666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>742.8995416666667</v>
+      </c>
+      <c r="I21" t="n">
+        <v>467.2952083333334</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.279125</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B22" t="n">
+        <v>17345.563625</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>174.2300833333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>652.3169166666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>601.4439583333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>607.5314166666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>965.618875</v>
+      </c>
+      <c r="I22" t="n">
+        <v>473.020875</v>
+      </c>
+      <c r="J22" t="n">
+        <v>36.26045833333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B23" t="n">
+        <v>17393.84370833333</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>193.3129583333333</v>
+      </c>
+      <c r="E23" t="n">
+        <v>651.74725</v>
+      </c>
+      <c r="F23" t="n">
+        <v>601.509875</v>
+      </c>
+      <c r="G23" t="n">
+        <v>479.7298333333333</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1073.323083333333</v>
+      </c>
+      <c r="I23" t="n">
+        <v>621.4419583333333</v>
+      </c>
+      <c r="J23" t="n">
+        <v>36.0735</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B24" t="n">
+        <v>18107.875375</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>167.976625</v>
+      </c>
+      <c r="E24" t="n">
+        <v>652.5202916666667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>590.3000416666666</v>
+      </c>
+      <c r="G24" t="n">
+        <v>538.2315</v>
+      </c>
+      <c r="H24" t="n">
+        <v>431.8802083333333</v>
+      </c>
+      <c r="I24" t="n">
+        <v>552.02</v>
+      </c>
+      <c r="J24" t="n">
+        <v>35.71195833333334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>residual_demand_mw</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rsa_contracted_demand_mw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unplanned_outages_mw</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46278</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6519.225583333333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6909.73225</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7060.312958333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7275.770666666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8195.647916666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8078.164249999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7415.309041666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7825.248666666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>20545.09083333333</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22046.701375</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8017.758083333333</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B11" t="n">
+        <v>20375.01329166667</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22009.86975</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8146.019416666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B12" t="n">
+        <v>20349.473</v>
+      </c>
+      <c r="C12" t="n">
+        <v>22016.05041666667</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7275.404916666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B13" t="n">
+        <v>19482.998125</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20979.59504166667</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6860.267</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B14" t="n">
+        <v>19487.81275</v>
+      </c>
+      <c r="C14" t="n">
+        <v>21272.60275</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7898.832916666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B15" t="n">
+        <v>19238.67066666667</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20781.39920833333</v>
+      </c>
+      <c r="D15" t="n">
+        <v>9190.43175</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17666.642625</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19897.02958333333</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8954.713833333333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B17" t="n">
+        <v>19681.941125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>21515.1505</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7141.410833333332</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B18" t="n">
+        <v>20481.45475</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22931.62358333333</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7637.729625</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B19" t="n">
+        <v>20850.805125</v>
+      </c>
+      <c r="C19" t="n">
+        <v>23450.45870833333</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8127.333416666667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B20" t="n">
+        <v>19957.53266666667</v>
+      </c>
+      <c r="C20" t="n">
+        <v>22001.31016666667</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8599.259749999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20358.61125</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21754.88029166666</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7592.623333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B22" t="n">
+        <v>19307.00045833333</v>
+      </c>
+      <c r="C22" t="n">
+        <v>20541.50345833333</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7320.809333333334</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B23" t="n">
+        <v>19161.67658333333</v>
+      </c>
+      <c r="C23" t="n">
+        <v>20407.15045833333</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8170.493833333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B24" t="n">
+        <v>20288.5225</v>
+      </c>
+      <c r="C24" t="n">
+        <v>21763.42270833334</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8735.369874999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B25" t="n">
+        <v>20073.65291666667</v>
+      </c>
+      <c r="C25" t="n">
+        <v>21804.49145833333</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7060.00375</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B26" t="n">
+        <v>20750.886125</v>
+      </c>
+      <c r="C26" t="n">
+        <v>21770.49829166667</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6569.93525</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>week_start</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>eaf_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>planned_outages_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unplanned_outages_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>other_outages_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B2" t="n">
+        <v>63.60801759626349</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16.25439581746905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19.96564396159935</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1719426246681096</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B3" t="n">
+        <v>62.26354655185958</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16.25394405043937</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.28298498634162</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1995244113594335</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58.14806178711437</v>
+      </c>
+      <c r="C4" t="n">
+        <v>16.83605281195734</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24.93616630455804</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07971909637025129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56.49017237680246</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16.61736210157978</v>
+      </c>
+      <c r="D5" t="n">
+        <v>26.47771084140147</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.414754680216278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B6" t="n">
+        <v>61.48087076801276</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12.9344304746393</v>
+      </c>
+      <c r="D6" t="n">
+        <v>25.5846937966108</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.96073715043171e-06</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B7" t="n">
+        <v>61.64690491551136</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13.44849295575325</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24.02505745137972</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8795446773556703</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B8" t="n">
+        <v>66.92968336395393</v>
+      </c>
+      <c r="C8" t="n">
+        <v>13.23125099466557</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19.67176464248445</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.167300998896047</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B9" t="n">
+        <v>68.09581106037895</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10.98435294108761</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.91906950169018</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0007664968432588366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B10" t="n">
+        <v>66.68931131118579</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.70358187885527</v>
+      </c>
+      <c r="D10" t="n">
+        <v>20.5959011972248</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0112056127341367</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B11" t="n">
+        <v>65.83665814779673</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12.5776900919222</v>
+      </c>
+      <c r="D11" t="n">
+        <v>21.54857459387429</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.03707716640679452</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B12" t="n">
+        <v>64.61325691531795</v>
+      </c>
+      <c r="C12" t="n">
+        <v>13.05439701358587</v>
+      </c>
+      <c r="D12" t="n">
+        <v>21.88952325049659</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4428228205996005</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B13" t="n">
+        <v>68.60639801630951</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.162821755426062</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22.0301226032337</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2006576250307212</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B14" t="n">
+        <v>67.06835662865282</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.838598387785607</v>
+      </c>
+      <c r="D14" t="n">
+        <v>22.93395572957585</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.159089253985713</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B15" t="n">
+        <v>70.1697484679632</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8.744624034041232</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20.98446727726543</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1011602207301399</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B16" t="n">
+        <v>73.85022238959466</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9.982809862247631</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15.86829043932489</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2986773088328317</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75.77742495688942</v>
+      </c>
+      <c r="C17" t="n">
+        <v>7.845951345996562</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.362925729455</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01369796765901555</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79.02425364828223</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7.160726322426761</v>
+      </c>
+      <c r="D18" t="n">
+        <v>13.80986953764923</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.005150491641787437</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B19" t="n">
+        <v>77.42775696114812</v>
+      </c>
+      <c r="C19" t="n">
+        <v>10.19960189454833</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12.36861754579994</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.00402359850362008</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B20" t="n">
+        <v>71.8740277332906</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11.86106039156081</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.04594489955642</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2189669755921659</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B21" t="n">
+        <v>72.03727613729306</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12.96603419786139</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14.88435741078731</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1123322540582355</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B22" t="n">
+        <v>70.39147305942008</v>
+      </c>
+      <c r="C22" t="n">
+        <v>15.1921513457951</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13.95175855613842</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4646170386464078</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B23" t="n">
+        <v>68.73701255091683</v>
+      </c>
+      <c r="C23" t="n">
+        <v>17.20810517719649</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13.59318204595909</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4617002259275844</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B24" t="n">
+        <v>66.7253877841638</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15.17899074753668</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18.07094475946948</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.02467670883004037</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B25" t="n">
+        <v>69.60439309456957</v>
+      </c>
+      <c r="C25" t="n">
+        <v>13.57951319659914</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.72716895196017</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.08892475687111907</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B26" t="n">
+        <v>71.48031312306077</v>
+      </c>
+      <c r="C26" t="n">
+        <v>12.78394940156672</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.72902901570654</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.006708459665970608</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B27" t="n">
+        <v>68.91712840754023</v>
+      </c>
+      <c r="C27" t="n">
+        <v>14.43823975869975</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.63057176087051</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.01406007288950761</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B28" t="n">
+        <v>71.26699172742431</v>
+      </c>
+      <c r="C28" t="n">
+        <v>12.6323334252563</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.9239722200921</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1767026272272886</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B29" t="n">
+        <v>70.8574684750094</v>
+      </c>
+      <c r="C29" t="n">
+        <v>13.75087457905506</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.11997922803058</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2716777179049559</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1644,1531 +3398,6 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>coal</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>gas</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>oil</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>nuclear</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>hydro</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pumped_storage</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>biomass</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B2" t="n">
-        <v>17693.9875</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>138.2768333333333</v>
-      </c>
-      <c r="E2" t="n">
-        <v>652.98425</v>
-      </c>
-      <c r="F2" t="n">
-        <v>301.9749166666667</v>
-      </c>
-      <c r="G2" t="n">
-        <v>484.1149166666667</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1278.61225</v>
-      </c>
-      <c r="I2" t="n">
-        <v>562.601125</v>
-      </c>
-      <c r="J2" t="n">
-        <v>45.88970833333334</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B3" t="n">
-        <v>17275.527</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>165.5623333333333</v>
-      </c>
-      <c r="E3" t="n">
-        <v>652.6445416666667</v>
-      </c>
-      <c r="F3" t="n">
-        <v>336.6506666666667</v>
-      </c>
-      <c r="G3" t="n">
-        <v>507.22575</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1594.529416666667</v>
-      </c>
-      <c r="I3" t="n">
-        <v>618.0322916666667</v>
-      </c>
-      <c r="J3" t="n">
-        <v>47.15379166666667</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B4" t="n">
-        <v>16370.0085</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>170.00225</v>
-      </c>
-      <c r="E4" t="n">
-        <v>652.5475</v>
-      </c>
-      <c r="F4" t="n">
-        <v>359.9209583333333</v>
-      </c>
-      <c r="G4" t="n">
-        <v>428.7385833333333</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2893.856708333333</v>
-      </c>
-      <c r="I4" t="n">
-        <v>876.8808749999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>46.64266666666666</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B5" t="n">
-        <v>17449.15991666667</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>153.4750833333333</v>
-      </c>
-      <c r="E5" t="n">
-        <v>653.47925</v>
-      </c>
-      <c r="F5" t="n">
-        <v>349.8301666666667</v>
-      </c>
-      <c r="G5" t="n">
-        <v>290.3386666666667</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3069.8105</v>
-      </c>
-      <c r="I5" t="n">
-        <v>367.928125</v>
-      </c>
-      <c r="J5" t="n">
-        <v>47.29916666666667</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B6" t="n">
-        <v>17407.89666666667</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0004166666666666667</v>
-      </c>
-      <c r="D6" t="n">
-        <v>112.4993333333333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>653.6539583333333</v>
-      </c>
-      <c r="F6" t="n">
-        <v>349.788375</v>
-      </c>
-      <c r="G6" t="n">
-        <v>481.446</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1491.586875</v>
-      </c>
-      <c r="I6" t="n">
-        <v>338.3531666666667</v>
-      </c>
-      <c r="J6" t="n">
-        <v>47.23795833333333</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B7" t="n">
-        <v>18280.72470833333</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8.333333333333333e-05</v>
-      </c>
-      <c r="D7" t="n">
-        <v>152.834875</v>
-      </c>
-      <c r="E7" t="n">
-        <v>653.3170416666667</v>
-      </c>
-      <c r="F7" t="n">
-        <v>380.742375</v>
-      </c>
-      <c r="G7" t="n">
-        <v>372.3356666666667</v>
-      </c>
-      <c r="H7" t="n">
-        <v>563.9242916666666</v>
-      </c>
-      <c r="I7" t="n">
-        <v>515.4672916666667</v>
-      </c>
-      <c r="J7" t="n">
-        <v>46.21925</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B8" t="n">
-        <v>18009.53429166667</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.002625</v>
-      </c>
-      <c r="D8" t="n">
-        <v>122.4090416666667</v>
-      </c>
-      <c r="E8" t="n">
-        <v>653.3082083333334</v>
-      </c>
-      <c r="F8" t="n">
-        <v>600.8853333333333</v>
-      </c>
-      <c r="G8" t="n">
-        <v>422.23925</v>
-      </c>
-      <c r="H8" t="n">
-        <v>687.1719583333334</v>
-      </c>
-      <c r="I8" t="n">
-        <v>781.8878333333333</v>
-      </c>
-      <c r="J8" t="n">
-        <v>46.63491666666667</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B9" t="n">
-        <v>17706.49125</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0007499999999999999</v>
-      </c>
-      <c r="D9" t="n">
-        <v>182.8252916666667</v>
-      </c>
-      <c r="E9" t="n">
-        <v>652.878875</v>
-      </c>
-      <c r="F9" t="n">
-        <v>599.8235000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>375.655375</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1102.776291666667</v>
-      </c>
-      <c r="I9" t="n">
-        <v>484.7176666666667</v>
-      </c>
-      <c r="J9" t="n">
-        <v>47.3625</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B10" t="n">
-        <v>17669.532875</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0002916666666666667</v>
-      </c>
-      <c r="D10" t="n">
-        <v>173.9636666666667</v>
-      </c>
-      <c r="E10" t="n">
-        <v>651.9264583333334</v>
-      </c>
-      <c r="F10" t="n">
-        <v>599.5548749999999</v>
-      </c>
-      <c r="G10" t="n">
-        <v>447.1493333333333</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1139.28375</v>
-      </c>
-      <c r="I10" t="n">
-        <v>479.9018333333333</v>
-      </c>
-      <c r="J10" t="n">
-        <v>47.39183333333333</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B11" t="n">
-        <v>16896.35883333334</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>160.5665416666667</v>
-      </c>
-      <c r="E11" t="n">
-        <v>651.2196250000001</v>
-      </c>
-      <c r="F11" t="n">
-        <v>600.0968333333334</v>
-      </c>
-      <c r="G11" t="n">
-        <v>419.5679166666666</v>
-      </c>
-      <c r="H11" t="n">
-        <v>890.0252083333334</v>
-      </c>
-      <c r="I11" t="n">
-        <v>544.627875</v>
-      </c>
-      <c r="J11" t="n">
-        <v>47.172125</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B12" t="n">
-        <v>16906.600875</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>122.7449583333333</v>
-      </c>
-      <c r="E12" t="n">
-        <v>650.5766666666667</v>
-      </c>
-      <c r="F12" t="n">
-        <v>600.951</v>
-      </c>
-      <c r="G12" t="n">
-        <v>376.0448333333333</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1137.985916666667</v>
-      </c>
-      <c r="I12" t="n">
-        <v>600.653</v>
-      </c>
-      <c r="J12" t="n">
-        <v>46.15108333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B13" t="n">
-        <v>16634.63670833334</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>146.1078333333333</v>
-      </c>
-      <c r="E13" t="n">
-        <v>651.1357916666667</v>
-      </c>
-      <c r="F13" t="n">
-        <v>601.398</v>
-      </c>
-      <c r="G13" t="n">
-        <v>409.3675</v>
-      </c>
-      <c r="H13" t="n">
-        <v>999.1999583333333</v>
-      </c>
-      <c r="I13" t="n">
-        <v>497.6774166666667</v>
-      </c>
-      <c r="J13" t="n">
-        <v>45.85116666666666</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15218.227</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>169.6042916666667</v>
-      </c>
-      <c r="E14" t="n">
-        <v>651.7128333333334</v>
-      </c>
-      <c r="F14" t="n">
-        <v>600.1207083333334</v>
-      </c>
-      <c r="G14" t="n">
-        <v>290.2275833333333</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1569.01675</v>
-      </c>
-      <c r="I14" t="n">
-        <v>614.9376666666667</v>
-      </c>
-      <c r="J14" t="n">
-        <v>46.43254166666667</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B15" t="n">
-        <v>17159.56579166666</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>165.1888333333333</v>
-      </c>
-      <c r="E15" t="n">
-        <v>653.1169583333334</v>
-      </c>
-      <c r="F15" t="n">
-        <v>599.3914166666667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>512.2461666666667</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1067.197791666667</v>
-      </c>
-      <c r="I15" t="n">
-        <v>719.6522083333333</v>
-      </c>
-      <c r="J15" t="n">
-        <v>46.359375</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B16" t="n">
-        <v>17998.38133333333</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>180.2736666666667</v>
-      </c>
-      <c r="E16" t="n">
-        <v>653.9607083333334</v>
-      </c>
-      <c r="F16" t="n">
-        <v>601.0589583333333</v>
-      </c>
-      <c r="G16" t="n">
-        <v>390.4469583333334</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1436.86225</v>
-      </c>
-      <c r="I16" t="n">
-        <v>966.917875</v>
-      </c>
-      <c r="J16" t="n">
-        <v>45.26491666666666</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B17" t="n">
-        <v>18143.19916666667</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>196.02275</v>
-      </c>
-      <c r="E17" t="n">
-        <v>653.6843749999999</v>
-      </c>
-      <c r="F17" t="n">
-        <v>602.0205833333333</v>
-      </c>
-      <c r="G17" t="n">
-        <v>554.88675</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1593.13</v>
-      </c>
-      <c r="I17" t="n">
-        <v>950.426875</v>
-      </c>
-      <c r="J17" t="n">
-        <v>44.47370833333333</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B18" t="n">
-        <v>17322.27058333333</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>177.8064166666667</v>
-      </c>
-      <c r="E18" t="n">
-        <v>652.6858333333333</v>
-      </c>
-      <c r="F18" t="n">
-        <v>590.4124166666667</v>
-      </c>
-      <c r="G18" t="n">
-        <v>458.717</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1375.421666666667</v>
-      </c>
-      <c r="I18" t="n">
-        <v>662.9270416666667</v>
-      </c>
-      <c r="J18" t="n">
-        <v>42.92879166666666</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B19" t="n">
-        <v>17702.08925</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>174.4282083333333</v>
-      </c>
-      <c r="E19" t="n">
-        <v>652.5819166666666</v>
-      </c>
-      <c r="F19" t="n">
-        <v>602.0305</v>
-      </c>
-      <c r="G19" t="n">
-        <v>437.2321666666667</v>
-      </c>
-      <c r="H19" t="n">
-        <v>811.6795416666668</v>
-      </c>
-      <c r="I19" t="n">
-        <v>581.4985416666667</v>
-      </c>
-      <c r="J19" t="n">
-        <v>40.59095833333333</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B20" t="n">
-        <v>16710.90104166667</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>163.2662083333333</v>
-      </c>
-      <c r="E20" t="n">
-        <v>651.898</v>
-      </c>
-      <c r="F20" t="n">
-        <v>601.0110833333333</v>
-      </c>
-      <c r="G20" t="n">
-        <v>354.256</v>
-      </c>
-      <c r="H20" t="n">
-        <v>760.618875</v>
-      </c>
-      <c r="I20" t="n">
-        <v>471.6087083333334</v>
-      </c>
-      <c r="J20" t="n">
-        <v>39.77541666666666</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B21" t="n">
-        <v>16824.019125</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>127.8207083333333</v>
-      </c>
-      <c r="E21" t="n">
-        <v>652.6476666666666</v>
-      </c>
-      <c r="F21" t="n">
-        <v>602.274375</v>
-      </c>
-      <c r="G21" t="n">
-        <v>254.3487916666667</v>
-      </c>
-      <c r="H21" t="n">
-        <v>736.4655833333333</v>
-      </c>
-      <c r="I21" t="n">
-        <v>522.2165</v>
-      </c>
-      <c r="J21" t="n">
-        <v>35.279125</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>residual_demand_mw</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rsa_contracted_demand_mw</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>unplanned_outages_mw</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46278</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6519.225583333333</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6909.73225</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="D4" t="n">
-        <v>7060.312958333333</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="D5" t="n">
-        <v>7275.770666666666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8195.647916666667</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8078.164249999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7415.309041666666</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7825.248666666666</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B10" t="n">
-        <v>20545.09083333333</v>
-      </c>
-      <c r="C10" t="n">
-        <v>22046.701375</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8017.758083333333</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B11" t="n">
-        <v>20375.01329166667</v>
-      </c>
-      <c r="C11" t="n">
-        <v>22009.86975</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8146.019416666666</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B12" t="n">
-        <v>20349.473</v>
-      </c>
-      <c r="C12" t="n">
-        <v>22016.05041666667</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7275.404916666666</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B13" t="n">
-        <v>19482.998125</v>
-      </c>
-      <c r="C13" t="n">
-        <v>20979.59504166667</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6860.267</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B14" t="n">
-        <v>19487.81275</v>
-      </c>
-      <c r="C14" t="n">
-        <v>21272.60275</v>
-      </c>
-      <c r="D14" t="n">
-        <v>7898.518291666667</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B15" t="n">
-        <v>19238.67066666667</v>
-      </c>
-      <c r="C15" t="n">
-        <v>20781.39920833333</v>
-      </c>
-      <c r="D15" t="n">
-        <v>9191.260958333332</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B16" t="n">
-        <v>17666.642625</v>
-      </c>
-      <c r="C16" t="n">
-        <v>19897.02958333333</v>
-      </c>
-      <c r="D16" t="n">
-        <v>8952.005333333333</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B17" t="n">
-        <v>19681.941125</v>
-      </c>
-      <c r="C17" t="n">
-        <v>21515.1505</v>
-      </c>
-      <c r="D17" t="n">
-        <v>7141.584416666666</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B18" t="n">
-        <v>20481.45475</v>
-      </c>
-      <c r="C18" t="n">
-        <v>22931.62358333333</v>
-      </c>
-      <c r="D18" t="n">
-        <v>7638.354583333334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B19" t="n">
-        <v>20850.805125</v>
-      </c>
-      <c r="C19" t="n">
-        <v>23450.45870833333</v>
-      </c>
-      <c r="D19" t="n">
-        <v>8129.333416666667</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B20" t="n">
-        <v>19957.53266666667</v>
-      </c>
-      <c r="C20" t="n">
-        <v>22001.31016666667</v>
-      </c>
-      <c r="D20" t="n">
-        <v>8604.014458333333</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B21" t="n">
-        <v>20358.61125</v>
-      </c>
-      <c r="C21" t="n">
-        <v>21754.88029166666</v>
-      </c>
-      <c r="D21" t="n">
-        <v>7610.065291666667</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B22" t="n">
-        <v>19307.00045833333</v>
-      </c>
-      <c r="C22" t="n">
-        <v>20541.50345833333</v>
-      </c>
-      <c r="D22" t="n">
-        <v>7244.538124999999</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B23" t="n">
-        <v>19161.67658333333</v>
-      </c>
-      <c r="C23" t="n">
-        <v>20405.49045833333</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8282.062124999999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B24" t="n">
-        <v>20288.5225</v>
-      </c>
-      <c r="C24" t="n">
-        <v>21737.09479166667</v>
-      </c>
-      <c r="D24" t="n">
-        <v>8869.295333333333</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>week_start</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>eaf_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>planned_outages_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>unplanned_outages_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>other_outages_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B2" t="n">
-        <v>63.60801759626349</v>
-      </c>
-      <c r="C2" t="n">
-        <v>16.25439581746905</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19.96564396159935</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.1719426246681096</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46118</v>
-      </c>
-      <c r="B3" t="n">
-        <v>62.26354655185958</v>
-      </c>
-      <c r="C3" t="n">
-        <v>16.25394405043937</v>
-      </c>
-      <c r="D3" t="n">
-        <v>21.28298498634162</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.1995244113594335</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46125</v>
-      </c>
-      <c r="B4" t="n">
-        <v>58.14806178711437</v>
-      </c>
-      <c r="C4" t="n">
-        <v>16.83605281195734</v>
-      </c>
-      <c r="D4" t="n">
-        <v>24.93616630455804</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.07971909637025129</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46132</v>
-      </c>
-      <c r="B5" t="n">
-        <v>56.49017237680246</v>
-      </c>
-      <c r="C5" t="n">
-        <v>16.61736210157978</v>
-      </c>
-      <c r="D5" t="n">
-        <v>26.47771084140147</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.414754680216278</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46139</v>
-      </c>
-      <c r="B6" t="n">
-        <v>61.48087076801276</v>
-      </c>
-      <c r="C6" t="n">
-        <v>12.9344304746393</v>
-      </c>
-      <c r="D6" t="n">
-        <v>25.5846937966108</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.96073715043171e-06</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46146</v>
-      </c>
-      <c r="B7" t="n">
-        <v>61.64690491551136</v>
-      </c>
-      <c r="C7" t="n">
-        <v>13.44849295575325</v>
-      </c>
-      <c r="D7" t="n">
-        <v>24.02505745137972</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8795446773556703</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46153</v>
-      </c>
-      <c r="B8" t="n">
-        <v>66.92968336395393</v>
-      </c>
-      <c r="C8" t="n">
-        <v>13.23125099466557</v>
-      </c>
-      <c r="D8" t="n">
-        <v>19.67176464248445</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.167300998896047</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B9" t="n">
-        <v>68.09581106037895</v>
-      </c>
-      <c r="C9" t="n">
-        <v>10.98435294108761</v>
-      </c>
-      <c r="D9" t="n">
-        <v>20.91906950169018</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0007664968432588366</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46167</v>
-      </c>
-      <c r="B10" t="n">
-        <v>66.68931131118579</v>
-      </c>
-      <c r="C10" t="n">
-        <v>12.70358187885527</v>
-      </c>
-      <c r="D10" t="n">
-        <v>20.5959011972248</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0112056127341367</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B11" t="n">
-        <v>65.83665814779673</v>
-      </c>
-      <c r="C11" t="n">
-        <v>12.5776900919222</v>
-      </c>
-      <c r="D11" t="n">
-        <v>21.54857459387429</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.03707716640679452</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46181</v>
-      </c>
-      <c r="B12" t="n">
-        <v>64.61325691531795</v>
-      </c>
-      <c r="C12" t="n">
-        <v>13.05439701358587</v>
-      </c>
-      <c r="D12" t="n">
-        <v>21.88952325049659</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4428228205996005</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46188</v>
-      </c>
-      <c r="B13" t="n">
-        <v>68.60639801630951</v>
-      </c>
-      <c r="C13" t="n">
-        <v>9.162821755426062</v>
-      </c>
-      <c r="D13" t="n">
-        <v>22.0301226032337</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.2006576250307212</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46195</v>
-      </c>
-      <c r="B14" t="n">
-        <v>67.06835662865282</v>
-      </c>
-      <c r="C14" t="n">
-        <v>9.838598387785604</v>
-      </c>
-      <c r="D14" t="n">
-        <v>22.93395572957585</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.159089253985713</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46202</v>
-      </c>
-      <c r="B15" t="n">
-        <v>70.1697484679632</v>
-      </c>
-      <c r="C15" t="n">
-        <v>8.744624034041232</v>
-      </c>
-      <c r="D15" t="n">
-        <v>20.98446727726543</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1011602207301399</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46209</v>
-      </c>
-      <c r="B16" t="n">
-        <v>73.85022238959466</v>
-      </c>
-      <c r="C16" t="n">
-        <v>9.982809862247631</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15.86829043932489</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2986773088328317</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46216</v>
-      </c>
-      <c r="B17" t="n">
-        <v>75.77742495688942</v>
-      </c>
-      <c r="C17" t="n">
-        <v>7.845951345996562</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.362925729455</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.01369796765901555</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79.02425364828223</v>
-      </c>
-      <c r="C18" t="n">
-        <v>7.160726322426761</v>
-      </c>
-      <c r="D18" t="n">
-        <v>13.80986953764923</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.005150491641787437</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="B19" t="n">
-        <v>77.42775696114812</v>
-      </c>
-      <c r="C19" t="n">
-        <v>10.19960189454833</v>
-      </c>
-      <c r="D19" t="n">
-        <v>12.36861754579994</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.00402359850362008</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="B20" t="n">
-        <v>71.8740277332906</v>
-      </c>
-      <c r="C20" t="n">
-        <v>11.86106039156081</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.04594489955642</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2189669755921659</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="B21" t="n">
-        <v>72.03727613729306</v>
-      </c>
-      <c r="C21" t="n">
-        <v>12.96603419786139</v>
-      </c>
-      <c r="D21" t="n">
-        <v>14.88435741078731</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.1123322540582355</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46251</v>
-      </c>
-      <c r="B22" t="n">
-        <v>70.3896680561767</v>
-      </c>
-      <c r="C22" t="n">
-        <v>15.1921513457951</v>
-      </c>
-      <c r="D22" t="n">
-        <v>13.95356355938179</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.4646170386464078</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46258</v>
-      </c>
-      <c r="B23" t="n">
-        <v>68.73381666525654</v>
-      </c>
-      <c r="C23" t="n">
-        <v>17.20810517719649</v>
-      </c>
-      <c r="D23" t="n">
-        <v>13.59637793161939</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4617002259275844</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B24" t="n">
-        <v>66.8088601288775</v>
-      </c>
-      <c r="C24" t="n">
-        <v>15.16842524139862</v>
-      </c>
-      <c r="D24" t="n">
-        <v>17.99803792089384</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.02467670883004037</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B25" t="n">
-        <v>69.81014911921082</v>
-      </c>
-      <c r="C25" t="n">
-        <v>13.51588603419731</v>
-      </c>
-      <c r="D25" t="n">
-        <v>16.58504008972074</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.08892475687111907</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B26" t="n">
-        <v>71.5610659156511</v>
-      </c>
-      <c r="C26" t="n">
-        <v>12.79342169490226</v>
-      </c>
-      <c r="D26" t="n">
-        <v>15.63880392978068</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.006708459665970608</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B27" t="n">
-        <v>69.08334612635622</v>
-      </c>
-      <c r="C27" t="n">
-        <v>14.42178210618627</v>
-      </c>
-      <c r="D27" t="n">
-        <v>16.480811694568</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.01406007288950761</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B28" t="n">
-        <v>71.46892750472888</v>
-      </c>
-      <c r="C28" t="n">
-        <v>12.45802183981612</v>
-      </c>
-      <c r="D28" t="n">
-        <v>15.82674218605601</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.2463084693989909</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
           <t>drakensberg_close_unit_hours</t>
         </is>
       </c>
@@ -3755,6 +3984,102 @@
       </c>
       <c r="J18" t="n">
         <v>60.81771720613288</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B19" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>84.50980392156863</v>
+      </c>
+      <c r="D19" t="n">
+        <v>84.50980392156863</v>
+      </c>
+      <c r="E19" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36.80597014925373</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36.80597014925373</v>
+      </c>
+      <c r="H19" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>64.90630323679727</v>
+      </c>
+      <c r="J19" t="n">
+        <v>61.49914821124361</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B20" t="n">
+        <v>82.59999999999998</v>
+      </c>
+      <c r="C20" t="n">
+        <v>80.98039215686272</v>
+      </c>
+      <c r="D20" t="n">
+        <v>80.98039215686272</v>
+      </c>
+      <c r="E20" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31.88059701492537</v>
+      </c>
+      <c r="G20" t="n">
+        <v>31.47761194029851</v>
+      </c>
+      <c r="H20" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>54.68483816013629</v>
+      </c>
+      <c r="J20" t="n">
+        <v>54.68483816013629</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B21" t="n">
+        <v>86.59999999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>84.9019607843137</v>
+      </c>
+      <c r="D21" t="n">
+        <v>80.98039215686272</v>
+      </c>
+      <c r="E21" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="F21" t="n">
+        <v>34.55223880597015</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33.86567164179105</v>
+      </c>
+      <c r="H21" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>62.86201022146507</v>
+      </c>
+      <c r="J21" t="n">
+        <v>54.68483816013629</v>
       </c>
     </row>
   </sheetData>
@@ -3768,7 +4093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4034,6 +4359,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
@@ -190,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$24</f>
+              <f>'Chart'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -218,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$24</f>
+              <f>'Chart'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -237,7 +237,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$24</f>
+              <f>'Chart'!$D$2:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -265,7 +265,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -274,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$24</f>
+              <f>'Chart'!$E$2:$E$30</f>
             </numRef>
           </val>
         </ser>
@@ -302,12 +302,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$24</f>
+              <f>'Chart'!$F$2:$F$30</f>
             </numRef>
           </val>
         </ser>
@@ -330,12 +330,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$24</f>
+              <f>'Chart'!$G$2:$G$30</f>
             </numRef>
           </val>
         </ser>
@@ -358,12 +358,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$24</f>
+              <f>'Chart'!$H$2:$H$30</f>
             </numRef>
           </val>
         </ser>
@@ -386,12 +386,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$24</f>
+              <f>'Chart'!$J$2:$J$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$24</f>
+              <f>'Chart'!$I$2:$I$30</f>
             </numRef>
           </val>
         </ser>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -995,12 +995,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>solar</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>nuclear</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>solar</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -1040,10 +1040,10 @@
         <v>1278.61225</v>
       </c>
       <c r="D2" t="n">
+        <v>562.601125</v>
+      </c>
+      <c r="E2" t="n">
         <v>652.98425</v>
-      </c>
-      <c r="E2" t="n">
-        <v>562.601125</v>
       </c>
       <c r="F2" t="n">
         <v>301.9749166666667</v>
@@ -1074,10 +1074,10 @@
         <v>1594.529416666667</v>
       </c>
       <c r="D3" t="n">
+        <v>618.0322916666667</v>
+      </c>
+      <c r="E3" t="n">
         <v>652.6445416666667</v>
-      </c>
-      <c r="E3" t="n">
-        <v>618.0322916666667</v>
       </c>
       <c r="F3" t="n">
         <v>336.6506666666667</v>
@@ -1103,10 +1103,10 @@
         <v>2893.856708333333</v>
       </c>
       <c r="D4" t="n">
+        <v>876.8808749999999</v>
+      </c>
+      <c r="E4" t="n">
         <v>652.5475</v>
-      </c>
-      <c r="E4" t="n">
-        <v>876.8808749999999</v>
       </c>
       <c r="F4" t="n">
         <v>359.9209583333333</v>
@@ -1132,10 +1132,10 @@
         <v>3069.8105</v>
       </c>
       <c r="D5" t="n">
+        <v>367.928125</v>
+      </c>
+      <c r="E5" t="n">
         <v>653.47925</v>
-      </c>
-      <c r="E5" t="n">
-        <v>367.928125</v>
       </c>
       <c r="F5" t="n">
         <v>349.8301666666667</v>
@@ -1161,10 +1161,10 @@
         <v>1491.586875</v>
       </c>
       <c r="D6" t="n">
+        <v>338.3531666666667</v>
+      </c>
+      <c r="E6" t="n">
         <v>653.6539583333333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>338.3531666666667</v>
       </c>
       <c r="F6" t="n">
         <v>349.788375</v>
@@ -1190,10 +1190,10 @@
         <v>563.9242916666666</v>
       </c>
       <c r="D7" t="n">
+        <v>515.4672916666667</v>
+      </c>
+      <c r="E7" t="n">
         <v>653.3170416666667</v>
-      </c>
-      <c r="E7" t="n">
-        <v>515.4672916666667</v>
       </c>
       <c r="F7" t="n">
         <v>380.742375</v>
@@ -1219,10 +1219,10 @@
         <v>687.1719583333334</v>
       </c>
       <c r="D8" t="n">
+        <v>781.8878333333333</v>
+      </c>
+      <c r="E8" t="n">
         <v>653.3082083333334</v>
-      </c>
-      <c r="E8" t="n">
-        <v>781.8878333333333</v>
       </c>
       <c r="F8" t="n">
         <v>600.8853333333333</v>
@@ -1248,10 +1248,10 @@
         <v>1102.776291666667</v>
       </c>
       <c r="D9" t="n">
+        <v>484.7176666666667</v>
+      </c>
+      <c r="E9" t="n">
         <v>652.878875</v>
-      </c>
-      <c r="E9" t="n">
-        <v>484.7176666666667</v>
       </c>
       <c r="F9" t="n">
         <v>599.8235000000001</v>
@@ -1277,10 +1277,10 @@
         <v>1139.28375</v>
       </c>
       <c r="D10" t="n">
+        <v>479.9018333333333</v>
+      </c>
+      <c r="E10" t="n">
         <v>651.9264583333334</v>
-      </c>
-      <c r="E10" t="n">
-        <v>479.9018333333333</v>
       </c>
       <c r="F10" t="n">
         <v>599.5548749999999</v>
@@ -1306,10 +1306,10 @@
         <v>890.0252083333334</v>
       </c>
       <c r="D11" t="n">
+        <v>544.627875</v>
+      </c>
+      <c r="E11" t="n">
         <v>651.2196250000001</v>
-      </c>
-      <c r="E11" t="n">
-        <v>544.627875</v>
       </c>
       <c r="F11" t="n">
         <v>600.0968333333334</v>
@@ -1335,10 +1335,10 @@
         <v>1137.985916666667</v>
       </c>
       <c r="D12" t="n">
+        <v>600.653</v>
+      </c>
+      <c r="E12" t="n">
         <v>650.5766666666667</v>
-      </c>
-      <c r="E12" t="n">
-        <v>600.653</v>
       </c>
       <c r="F12" t="n">
         <v>600.951</v>
@@ -1364,10 +1364,10 @@
         <v>999.1999583333333</v>
       </c>
       <c r="D13" t="n">
+        <v>497.6774166666667</v>
+      </c>
+      <c r="E13" t="n">
         <v>651.1357916666667</v>
-      </c>
-      <c r="E13" t="n">
-        <v>497.6774166666667</v>
       </c>
       <c r="F13" t="n">
         <v>601.398</v>
@@ -1393,10 +1393,10 @@
         <v>1569.01675</v>
       </c>
       <c r="D14" t="n">
+        <v>614.9376666666667</v>
+      </c>
+      <c r="E14" t="n">
         <v>651.7128333333334</v>
-      </c>
-      <c r="E14" t="n">
-        <v>614.9376666666667</v>
       </c>
       <c r="F14" t="n">
         <v>600.1207083333334</v>
@@ -1422,10 +1422,10 @@
         <v>1067.197791666667</v>
       </c>
       <c r="D15" t="n">
+        <v>719.6522083333333</v>
+      </c>
+      <c r="E15" t="n">
         <v>653.1169583333334</v>
-      </c>
-      <c r="E15" t="n">
-        <v>719.6522083333333</v>
       </c>
       <c r="F15" t="n">
         <v>599.3914166666667</v>
@@ -1451,10 +1451,10 @@
         <v>1436.86225</v>
       </c>
       <c r="D16" t="n">
+        <v>966.917875</v>
+      </c>
+      <c r="E16" t="n">
         <v>653.9607083333334</v>
-      </c>
-      <c r="E16" t="n">
-        <v>966.917875</v>
       </c>
       <c r="F16" t="n">
         <v>601.0589583333333</v>
@@ -1480,10 +1480,10 @@
         <v>1593.13</v>
       </c>
       <c r="D17" t="n">
+        <v>950.426875</v>
+      </c>
+      <c r="E17" t="n">
         <v>653.6843749999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>950.426875</v>
       </c>
       <c r="F17" t="n">
         <v>602.0205833333333</v>
@@ -1509,10 +1509,10 @@
         <v>1375.421666666667</v>
       </c>
       <c r="D18" t="n">
+        <v>662.9270416666667</v>
+      </c>
+      <c r="E18" t="n">
         <v>652.6858333333333</v>
-      </c>
-      <c r="E18" t="n">
-        <v>662.9270416666667</v>
       </c>
       <c r="F18" t="n">
         <v>590.4124166666667</v>
@@ -1543,10 +1543,10 @@
         <v>811.6795416666668</v>
       </c>
       <c r="D19" t="n">
+        <v>543.9985416666667</v>
+      </c>
+      <c r="E19" t="n">
         <v>652.5819166666666</v>
-      </c>
-      <c r="E19" t="n">
-        <v>543.9985416666667</v>
       </c>
       <c r="F19" t="n">
         <v>602.0305</v>
@@ -1572,10 +1572,10 @@
         <v>760.618875</v>
       </c>
       <c r="D20" t="n">
+        <v>434.1087083333334</v>
+      </c>
+      <c r="E20" t="n">
         <v>651.898</v>
-      </c>
-      <c r="E20" t="n">
-        <v>434.1087083333334</v>
       </c>
       <c r="F20" t="n">
         <v>601.0110833333333</v>
@@ -1601,10 +1601,10 @@
         <v>742.8995416666667</v>
       </c>
       <c r="D21" t="n">
+        <v>467.2952083333334</v>
+      </c>
+      <c r="E21" t="n">
         <v>652.6476666666666</v>
-      </c>
-      <c r="E21" t="n">
-        <v>467.2952083333334</v>
       </c>
       <c r="F21" t="n">
         <v>602.274375</v>
@@ -1630,10 +1630,10 @@
         <v>965.618875</v>
       </c>
       <c r="D22" t="n">
+        <v>473.020875</v>
+      </c>
+      <c r="E22" t="n">
         <v>652.3169166666667</v>
-      </c>
-      <c r="E22" t="n">
-        <v>473.020875</v>
       </c>
       <c r="F22" t="n">
         <v>601.4439583333334</v>
@@ -1659,10 +1659,10 @@
         <v>1073.323083333333</v>
       </c>
       <c r="D23" t="n">
+        <v>621.4419583333333</v>
+      </c>
+      <c r="E23" t="n">
         <v>651.74725</v>
-      </c>
-      <c r="E23" t="n">
-        <v>621.4419583333333</v>
       </c>
       <c r="F23" t="n">
         <v>601.509875</v>
@@ -1688,10 +1688,10 @@
         <v>431.8802083333333</v>
       </c>
       <c r="D24" t="n">
+        <v>552.02</v>
+      </c>
+      <c r="E24" t="n">
         <v>652.5202916666667</v>
-      </c>
-      <c r="E24" t="n">
-        <v>552.02</v>
       </c>
       <c r="F24" t="n">
         <v>590.3000416666666</v>
@@ -1704,6 +1704,180 @@
       </c>
       <c r="I24" t="n">
         <v>35.71195833333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B25" t="n">
+        <v>17473.37695833333</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1273.554791666667</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1142.845</v>
+      </c>
+      <c r="E25" t="n">
+        <v>142.962875</v>
+      </c>
+      <c r="F25" t="n">
+        <v>354.3287500000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>458.746875</v>
+      </c>
+      <c r="H25" t="n">
+        <v>285.3403333333333</v>
+      </c>
+      <c r="I25" t="n">
+        <v>45.00108333333333</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16686.938375</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1915.222708333333</v>
+      </c>
+      <c r="D26" t="n">
+        <v>753.7136666666665</v>
+      </c>
+      <c r="E26" t="n">
+        <v>444.1028750000001</v>
+      </c>
+      <c r="F26" t="n">
+        <v>170.4502083333333</v>
+      </c>
+      <c r="G26" t="n">
+        <v>506.46825</v>
+      </c>
+      <c r="H26" t="n">
+        <v>177.3490833333334</v>
+      </c>
+      <c r="I26" t="n">
+        <v>45.0365</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B27" t="n">
+        <v>17242.19420833333</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1642.047208333333</v>
+      </c>
+      <c r="D27" t="n">
+        <v>814.2414583333334</v>
+      </c>
+      <c r="E27" t="n">
+        <v>641.2096666666667</v>
+      </c>
+      <c r="F27" t="n">
+        <v>164.662375</v>
+      </c>
+      <c r="G27" t="n">
+        <v>491.703875</v>
+      </c>
+      <c r="H27" t="n">
+        <v>173.5791666666667</v>
+      </c>
+      <c r="I27" t="n">
+        <v>46.19295833333334</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B28" t="n">
+        <v>17503.25941666666</v>
+      </c>
+      <c r="C28" t="n">
+        <v>738.0077083333334</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1324.971625</v>
+      </c>
+      <c r="E28" t="n">
+        <v>642.1610833333335</v>
+      </c>
+      <c r="F28" t="n">
+        <v>156.1151249999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>525.5889999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>167.515125</v>
+      </c>
+      <c r="I28" t="n">
+        <v>45.93404166666667</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B29" t="n">
+        <v>17151.06870833333</v>
+      </c>
+      <c r="C29" t="n">
+        <v>862.9756666666668</v>
+      </c>
+      <c r="D29" t="n">
+        <v>712.8272916666666</v>
+      </c>
+      <c r="E29" t="n">
+        <v>643.2409583333333</v>
+      </c>
+      <c r="F29" t="n">
+        <v>163.5421666666666</v>
+      </c>
+      <c r="G29" t="n">
+        <v>389.2474999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>172.0419166666667</v>
+      </c>
+      <c r="I29" t="n">
+        <v>46.29941666666667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B30" t="n">
+        <v>16217.91733333333</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1326.257708333333</v>
+      </c>
+      <c r="D30" t="n">
+        <v>708.0332083333334</v>
+      </c>
+      <c r="E30" t="n">
+        <v>645.8448333333333</v>
+      </c>
+      <c r="F30" t="n">
+        <v>157.4335416666667</v>
+      </c>
+      <c r="G30" t="n">
+        <v>394.0407083333333</v>
+      </c>
+      <c r="H30" t="n">
+        <v>165.051</v>
+      </c>
+      <c r="I30" t="n">
+        <v>45.30591666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1718,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2510,6 +2684,198 @@
       </c>
       <c r="J24" t="n">
         <v>35.71195833333334</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B25" t="n">
+        <v>17473.37695833333</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5228333333333333</v>
+      </c>
+      <c r="D25" t="n">
+        <v>285.3403333333333</v>
+      </c>
+      <c r="E25" t="n">
+        <v>142.962875</v>
+      </c>
+      <c r="F25" t="n">
+        <v>354.3287500000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>458.746875</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1273.554791666667</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1142.845</v>
+      </c>
+      <c r="J25" t="n">
+        <v>44.47825</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B26" t="n">
+        <v>16686.938375</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8.333333333333333e-05</v>
+      </c>
+      <c r="D26" t="n">
+        <v>177.3490833333334</v>
+      </c>
+      <c r="E26" t="n">
+        <v>444.1028750000001</v>
+      </c>
+      <c r="F26" t="n">
+        <v>170.4502083333333</v>
+      </c>
+      <c r="G26" t="n">
+        <v>506.46825</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1915.222708333333</v>
+      </c>
+      <c r="I26" t="n">
+        <v>753.7136666666665</v>
+      </c>
+      <c r="J26" t="n">
+        <v>45.03641666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B27" t="n">
+        <v>17242.19420833333</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.3720416666666667</v>
+      </c>
+      <c r="D27" t="n">
+        <v>173.5791666666667</v>
+      </c>
+      <c r="E27" t="n">
+        <v>641.2096666666667</v>
+      </c>
+      <c r="F27" t="n">
+        <v>164.662375</v>
+      </c>
+      <c r="G27" t="n">
+        <v>491.703875</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1642.047208333333</v>
+      </c>
+      <c r="I27" t="n">
+        <v>814.2414583333334</v>
+      </c>
+      <c r="J27" t="n">
+        <v>45.82091666666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B28" t="n">
+        <v>17503.25941666666</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0001666666666666667</v>
+      </c>
+      <c r="D28" t="n">
+        <v>167.515125</v>
+      </c>
+      <c r="E28" t="n">
+        <v>642.1610833333335</v>
+      </c>
+      <c r="F28" t="n">
+        <v>156.1151249999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>525.5889999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>738.0077083333334</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1324.971625</v>
+      </c>
+      <c r="J28" t="n">
+        <v>45.93387500000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B29" t="n">
+        <v>17151.06870833333</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="D29" t="n">
+        <v>172.0419166666667</v>
+      </c>
+      <c r="E29" t="n">
+        <v>643.2409583333333</v>
+      </c>
+      <c r="F29" t="n">
+        <v>163.5421666666666</v>
+      </c>
+      <c r="G29" t="n">
+        <v>389.2474999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>862.9756666666668</v>
+      </c>
+      <c r="I29" t="n">
+        <v>712.8272916666666</v>
+      </c>
+      <c r="J29" t="n">
+        <v>45.90066666666667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B30" t="n">
+        <v>16217.91733333333</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.000125</v>
+      </c>
+      <c r="D30" t="n">
+        <v>165.051</v>
+      </c>
+      <c r="E30" t="n">
+        <v>645.8448333333333</v>
+      </c>
+      <c r="F30" t="n">
+        <v>157.4335416666667</v>
+      </c>
+      <c r="G30" t="n">
+        <v>394.0407083333333</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1326.257708333333</v>
+      </c>
+      <c r="I30" t="n">
+        <v>708.0332083333334</v>
+      </c>
+      <c r="J30" t="n">
+        <v>45.30579166666667</v>
       </c>
     </row>
   </sheetData>
@@ -2523,7 +2889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2851,6 +3217,140 @@
       </c>
       <c r="D26" t="n">
         <v>6569.93525</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8583.199958333333</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8596.019208333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8051.565041666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8816.028458333334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8524.979374999997</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10122.000375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11791.06633333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D34" t="n">
+        <v>12527.55491666667</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B35" t="n">
+        <v>18858.80116666666</v>
+      </c>
+      <c r="C35" t="n">
+        <v>21572.77395833334</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11261.56220833333</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B36" t="n">
+        <v>19581.89741666666</v>
+      </c>
+      <c r="C36" t="n">
+        <v>22084.007</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11609.65154166667</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B37" t="n">
+        <v>19970.7475</v>
+      </c>
+      <c r="C37" t="n">
+        <v>22079.66070833334</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8979.143875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B38" t="n">
+        <v>19313.90845833334</v>
+      </c>
+      <c r="C38" t="n">
+        <v>20935.61208333333</v>
+      </c>
+      <c r="D38" t="n">
+        <v>7781.862416666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B39" t="n">
+        <v>18446.27329166667</v>
+      </c>
+      <c r="C39" t="n">
+        <v>20525.87</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7427.636833333334</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2945,7 +3445,7 @@
         <v>24.93616630455804</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07971909637025129</v>
+        <v>0.07971909637025131</v>
       </c>
     </row>
     <row r="5">
@@ -2962,7 +3462,7 @@
         <v>26.47771084140147</v>
       </c>
       <c r="E5" t="n">
-        <v>0.414754680216278</v>
+        <v>0.4147546802162781</v>
       </c>
     </row>
     <row r="6">
@@ -2976,7 +3476,7 @@
         <v>12.9344304746393</v>
       </c>
       <c r="D6" t="n">
-        <v>25.5846937966108</v>
+        <v>25.58469379661079</v>
       </c>
       <c r="E6" t="n">
         <v>4.96073715043171e-06</v>
@@ -3013,7 +3513,7 @@
         <v>19.67176464248445</v>
       </c>
       <c r="E8" t="n">
-        <v>0.167300998896047</v>
+        <v>0.1673009988960471</v>
       </c>
     </row>
     <row r="9">
@@ -3038,7 +3538,7 @@
         <v>46167</v>
       </c>
       <c r="B10" t="n">
-        <v>66.68931131118579</v>
+        <v>66.68931131118578</v>
       </c>
       <c r="C10" t="n">
         <v>12.70358187885527</v>
@@ -3047,7 +3547,7 @@
         <v>20.5959011972248</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0112056127341367</v>
+        <v>0.01120561273413672</v>
       </c>
     </row>
     <row r="11">
@@ -3058,7 +3558,7 @@
         <v>65.83665814779673</v>
       </c>
       <c r="C11" t="n">
-        <v>12.5776900919222</v>
+        <v>12.57769009192219</v>
       </c>
       <c r="D11" t="n">
         <v>21.54857459387429</v>
@@ -3098,7 +3598,7 @@
         <v>22.0301226032337</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2006576250307212</v>
+        <v>0.2006576250307213</v>
       </c>
     </row>
     <row r="14">
@@ -3109,13 +3609,13 @@
         <v>67.06835662865282</v>
       </c>
       <c r="C14" t="n">
-        <v>9.838598387785607</v>
+        <v>9.838598387785609</v>
       </c>
       <c r="D14" t="n">
         <v>22.93395572957585</v>
       </c>
       <c r="E14" t="n">
-        <v>0.159089253985713</v>
+        <v>0.1590892539857131</v>
       </c>
     </row>
     <row r="15">
@@ -3140,7 +3640,7 @@
         <v>46209</v>
       </c>
       <c r="B16" t="n">
-        <v>73.85022238959466</v>
+        <v>73.85022238959465</v>
       </c>
       <c r="C16" t="n">
         <v>9.982809862247631</v>
@@ -3157,7 +3657,7 @@
         <v>46216</v>
       </c>
       <c r="B17" t="n">
-        <v>75.77742495688942</v>
+        <v>75.77742495688943</v>
       </c>
       <c r="C17" t="n">
         <v>7.845951345996562</v>
@@ -3177,7 +3677,7 @@
         <v>79.02425364828223</v>
       </c>
       <c r="C18" t="n">
-        <v>7.160726322426761</v>
+        <v>7.160726322426762</v>
       </c>
       <c r="D18" t="n">
         <v>13.80986953764923</v>
@@ -3200,7 +3700,7 @@
         <v>12.36861754579994</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00402359850362008</v>
+        <v>0.004023598503620079</v>
       </c>
     </row>
     <row r="20">
@@ -3217,7 +3717,7 @@
         <v>16.04594489955642</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2189669755921659</v>
+        <v>0.218966975592166</v>
       </c>
     </row>
     <row r="21">
@@ -3242,16 +3742,16 @@
         <v>46251</v>
       </c>
       <c r="B22" t="n">
-        <v>70.39147305942008</v>
+        <v>70.38217500120871</v>
       </c>
       <c r="C22" t="n">
-        <v>15.1921513457951</v>
+        <v>15.19215134579511</v>
       </c>
       <c r="D22" t="n">
-        <v>13.95175855613842</v>
+        <v>13.96105661434978</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4646170386464078</v>
+        <v>0.4646170386464079</v>
       </c>
     </row>
     <row r="23">
@@ -3259,13 +3759,13 @@
         <v>46258</v>
       </c>
       <c r="B23" t="n">
-        <v>68.73701255091683</v>
+        <v>68.73002823591153</v>
       </c>
       <c r="C23" t="n">
         <v>17.20810517719649</v>
       </c>
       <c r="D23" t="n">
-        <v>13.59318204595909</v>
+        <v>13.60016636096439</v>
       </c>
       <c r="E23" t="n">
         <v>0.4617002259275844</v>
@@ -3276,13 +3776,13 @@
         <v>46265</v>
       </c>
       <c r="B24" t="n">
-        <v>66.7253877841638</v>
+        <v>66.72482359994713</v>
       </c>
       <c r="C24" t="n">
         <v>15.17899074753668</v>
       </c>
       <c r="D24" t="n">
-        <v>18.07094475946948</v>
+        <v>18.07150894368615</v>
       </c>
       <c r="E24" t="n">
         <v>0.02467670883004037</v>
@@ -3293,13 +3793,13 @@
         <v>46272</v>
       </c>
       <c r="B25" t="n">
-        <v>69.60439309456957</v>
+        <v>69.60495248516452</v>
       </c>
       <c r="C25" t="n">
         <v>13.57951319659914</v>
       </c>
       <c r="D25" t="n">
-        <v>16.72716895196017</v>
+        <v>16.72660956136521</v>
       </c>
       <c r="E25" t="n">
         <v>0.08892475687111907</v>
@@ -3310,13 +3810,13 @@
         <v>46279</v>
       </c>
       <c r="B26" t="n">
-        <v>71.48031312306077</v>
+        <v>71.47255213310446</v>
       </c>
       <c r="C26" t="n">
         <v>12.78394940156672</v>
       </c>
       <c r="D26" t="n">
-        <v>15.72902901570654</v>
+        <v>15.73679000566285</v>
       </c>
       <c r="E26" t="n">
         <v>0.006708459665970608</v>
@@ -3327,13 +3827,13 @@
         <v>46286</v>
       </c>
       <c r="B27" t="n">
-        <v>68.91712840754023</v>
+        <v>68.91680060629835</v>
       </c>
       <c r="C27" t="n">
         <v>14.43823975869975</v>
       </c>
       <c r="D27" t="n">
-        <v>16.63057176087051</v>
+        <v>16.63089956211239</v>
       </c>
       <c r="E27" t="n">
         <v>0.01406007288950761</v>
@@ -3344,16 +3844,16 @@
         <v>46293</v>
       </c>
       <c r="B28" t="n">
-        <v>71.26699172742431</v>
+        <v>70.77904214053693</v>
       </c>
       <c r="C28" t="n">
-        <v>12.6323334252563</v>
+        <v>12.64205941615643</v>
       </c>
       <c r="D28" t="n">
-        <v>15.9239722200921</v>
+        <v>16.40219581607935</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1767026272272886</v>
+        <v>0.1767026272272887</v>
       </c>
     </row>
     <row r="29">
@@ -3361,16 +3861,50 @@
         <v>46300</v>
       </c>
       <c r="B29" t="n">
-        <v>70.8574684750094</v>
+        <v>69.45402180196547</v>
       </c>
       <c r="C29" t="n">
-        <v>13.75087457905506</v>
+        <v>13.8353926782126</v>
       </c>
       <c r="D29" t="n">
-        <v>15.11997922803058</v>
+        <v>16.52173378518143</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2716777179049559</v>
+        <v>0.1888517346405075</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B30" t="n">
+        <v>68.83048738344954</v>
+      </c>
+      <c r="C30" t="n">
+        <v>13.1267393226801</v>
+      </c>
+      <c r="D30" t="n">
+        <v>18.04277329387036</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B31" t="n">
+        <v>65.445539118385</v>
+      </c>
+      <c r="C31" t="n">
+        <v>13.50209187430443</v>
+      </c>
+      <c r="D31" t="n">
+        <v>21.0146773700396</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.03769163727097908</v>
       </c>
     </row>
   </sheetData>
@@ -3384,7 +3918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4080,6 +4614,326 @@
       </c>
       <c r="J21" t="n">
         <v>54.68483816013629</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>86.07843137254902</v>
+      </c>
+      <c r="D22" t="n">
+        <v>86.07843137254902</v>
+      </c>
+      <c r="E22" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="F22" t="n">
+        <v>47.95522388059702</v>
+      </c>
+      <c r="G22" t="n">
+        <v>42.2089552238806</v>
+      </c>
+      <c r="H22" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>73.76490630323678</v>
+      </c>
+      <c r="J22" t="n">
+        <v>72.40204429301534</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>85.68627450980392</v>
+      </c>
+      <c r="D23" t="n">
+        <v>85.68627450980392</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="F23" t="n">
+        <v>47.20895522388059</v>
+      </c>
+      <c r="G23" t="n">
+        <v>41.73134328358209</v>
+      </c>
+      <c r="H23" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>68.65417376490629</v>
+      </c>
+      <c r="J23" t="n">
+        <v>67.6320272572402</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B24" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>87.64705882352942</v>
+      </c>
+      <c r="D24" t="n">
+        <v>86.07843137254902</v>
+      </c>
+      <c r="E24" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.05970149253731</v>
+      </c>
+      <c r="G24" t="n">
+        <v>42.68656716417911</v>
+      </c>
+      <c r="H24" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>69.6763202725724</v>
+      </c>
+      <c r="J24" t="n">
+        <v>69.6763202725724</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>89.01960784313725</v>
+      </c>
+      <c r="D25" t="n">
+        <v>87.64705882352942</v>
+      </c>
+      <c r="E25" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="F25" t="n">
+        <v>44.1044776119403</v>
+      </c>
+      <c r="G25" t="n">
+        <v>44.1044776119403</v>
+      </c>
+      <c r="H25" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>74.44633730834754</v>
+      </c>
+      <c r="J25" t="n">
+        <v>71.03918228279386</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B26" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>84.90196078431373</v>
+      </c>
+      <c r="D26" t="n">
+        <v>84.50980392156863</v>
+      </c>
+      <c r="E26" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>36.11940298507463</v>
+      </c>
+      <c r="G26" t="n">
+        <v>34.25373134328358</v>
+      </c>
+      <c r="H26" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>60.81771720613288</v>
+      </c>
+      <c r="J26" t="n">
+        <v>60.47700170357751</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B27" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>84.50980392156863</v>
+      </c>
+      <c r="D27" t="n">
+        <v>84.50980392156863</v>
+      </c>
+      <c r="E27" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>38.46268656716418</v>
+      </c>
+      <c r="G27" t="n">
+        <v>38.46268656716418</v>
+      </c>
+      <c r="H27" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>71.03918228279386</v>
+      </c>
+      <c r="J27" t="n">
+        <v>62.52129471890972</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B28" t="n">
+        <v>75</v>
+      </c>
+      <c r="C28" t="n">
+        <v>73.52941176470588</v>
+      </c>
+      <c r="D28" t="n">
+        <v>73.52941176470588</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26.48</v>
+      </c>
+      <c r="F28" t="n">
+        <v>39.52238805970149</v>
+      </c>
+      <c r="G28" t="n">
+        <v>33.07462686567164</v>
+      </c>
+      <c r="H28" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>55.36626916524702</v>
+      </c>
+      <c r="J28" t="n">
+        <v>55.36626916524702</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B29" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>73.13725490196077</v>
+      </c>
+      <c r="D29" t="n">
+        <v>73.13725490196077</v>
+      </c>
+      <c r="E29" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="F29" t="n">
+        <v>38.07462686567165</v>
+      </c>
+      <c r="G29" t="n">
+        <v>37.77611940298507</v>
+      </c>
+      <c r="H29" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>58.09199318568995</v>
+      </c>
+      <c r="J29" t="n">
+        <v>58.09199318568995</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B30" t="n">
+        <v>81</v>
+      </c>
+      <c r="C30" t="n">
+        <v>79.41176470588235</v>
+      </c>
+      <c r="D30" t="n">
+        <v>73.52941176470588</v>
+      </c>
+      <c r="E30" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="F30" t="n">
+        <v>52.94029850746268</v>
+      </c>
+      <c r="G30" t="n">
+        <v>38.35820895522388</v>
+      </c>
+      <c r="H30" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>72.40204429301534</v>
+      </c>
+      <c r="J30" t="n">
+        <v>57.41056218057922</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83</v>
+      </c>
+      <c r="C31" t="n">
+        <v>81.37254901960785</v>
+      </c>
+      <c r="D31" t="n">
+        <v>80.58823529411765</v>
+      </c>
+      <c r="E31" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="F31" t="n">
+        <v>39.71641791044776</v>
+      </c>
+      <c r="G31" t="n">
+        <v>39.71641791044776</v>
+      </c>
+      <c r="H31" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>69.6763202725724</v>
+      </c>
+      <c r="J31" t="n">
+        <v>69.6763202725724</v>
       </c>
     </row>
   </sheetData>
@@ -4093,7 +4947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4401,6 +5255,146 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
+++ b/output/Data and Chart Outputs/south_africa_generation_mix_daily.xlsx
@@ -190,12 +190,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$30</f>
+              <f>'Chart'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -218,12 +218,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$30</f>
+              <f>'Chart'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -246,12 +246,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$30</f>
+              <f>'Chart'!$D$2:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -274,12 +274,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$30</f>
+              <f>'Chart'!$E$2:$E$32</f>
             </numRef>
           </val>
         </ser>
@@ -302,12 +302,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$30</f>
+              <f>'Chart'!$F$2:$F$32</f>
             </numRef>
           </val>
         </ser>
@@ -330,12 +330,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$30</f>
+              <f>'Chart'!$G$2:$G$32</f>
             </numRef>
           </val>
         </ser>
@@ -358,12 +358,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$30</f>
+              <f>'Chart'!$H$2:$H$32</f>
             </numRef>
           </val>
         </ser>
@@ -386,12 +386,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$J$2:$J$30</f>
+              <f>'Chart'!$J$2:$J$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$30</f>
+              <f>'Chart'!$I$2:$I$32</f>
             </numRef>
           </val>
         </ser>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1804,7 +1804,7 @@
         <v>738.0077083333334</v>
       </c>
       <c r="D28" t="n">
-        <v>1324.971625</v>
+        <v>1332.997958333333</v>
       </c>
       <c r="E28" t="n">
         <v>642.1610833333335</v>
@@ -1830,10 +1830,10 @@
         <v>17151.06870833333</v>
       </c>
       <c r="C29" t="n">
-        <v>862.9756666666668</v>
+        <v>863.7875416666666</v>
       </c>
       <c r="D29" t="n">
-        <v>712.8272916666666</v>
+        <v>720.2216666666667</v>
       </c>
       <c r="E29" t="n">
         <v>643.2409583333333</v>
@@ -1859,10 +1859,10 @@
         <v>16217.91733333333</v>
       </c>
       <c r="C30" t="n">
-        <v>1326.257708333333</v>
+        <v>1327.181791666667</v>
       </c>
       <c r="D30" t="n">
-        <v>708.0332083333334</v>
+        <v>713.5360833333333</v>
       </c>
       <c r="E30" t="n">
         <v>645.8448333333333</v>
@@ -1877,7 +1877,65 @@
         <v>165.051</v>
       </c>
       <c r="I30" t="n">
-        <v>45.30591666666667</v>
+        <v>45.30737500000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B31" t="n">
+        <v>16977.26729166667</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1516.055333333333</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1048.055458333333</v>
+      </c>
+      <c r="E31" t="n">
+        <v>646.6200416666667</v>
+      </c>
+      <c r="F31" t="n">
+        <v>212.0034999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>508.8252499999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>171.8432083333333</v>
+      </c>
+      <c r="I31" t="n">
+        <v>45.83712500000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B32" t="n">
+        <v>17856.313375</v>
+      </c>
+      <c r="C32" t="n">
+        <v>926.1660416666667</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1073.66325</v>
+      </c>
+      <c r="E32" t="n">
+        <v>648.24325</v>
+      </c>
+      <c r="F32" t="n">
+        <v>269.1196666666666</v>
+      </c>
+      <c r="G32" t="n">
+        <v>369.5902916666666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>172.7859166666667</v>
+      </c>
+      <c r="I32" t="n">
+        <v>45.962875</v>
       </c>
     </row>
   </sheetData>
@@ -1892,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2808,7 +2866,7 @@
         <v>738.0077083333334</v>
       </c>
       <c r="I28" t="n">
-        <v>1324.971625</v>
+        <v>1332.997958333333</v>
       </c>
       <c r="J28" t="n">
         <v>45.93387500000001</v>
@@ -2837,10 +2895,10 @@
         <v>389.2474999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>862.9756666666668</v>
+        <v>863.7875416666666</v>
       </c>
       <c r="I29" t="n">
-        <v>712.8272916666666</v>
+        <v>720.2216666666667</v>
       </c>
       <c r="J29" t="n">
         <v>45.90066666666667</v>
@@ -2869,13 +2927,77 @@
         <v>394.0407083333333</v>
       </c>
       <c r="H30" t="n">
-        <v>1326.257708333333</v>
+        <v>1327.181791666667</v>
       </c>
       <c r="I30" t="n">
-        <v>708.0332083333334</v>
+        <v>713.5360833333333</v>
       </c>
       <c r="J30" t="n">
-        <v>45.30579166666667</v>
+        <v>45.30725000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B31" t="n">
+        <v>16977.26729166667</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001291666666666667</v>
+      </c>
+      <c r="D31" t="n">
+        <v>171.8432083333333</v>
+      </c>
+      <c r="E31" t="n">
+        <v>646.6200416666667</v>
+      </c>
+      <c r="F31" t="n">
+        <v>212.0034999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>508.8252499999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1516.055333333333</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1048.055458333333</v>
+      </c>
+      <c r="J31" t="n">
+        <v>45.83583333333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B32" t="n">
+        <v>17856.313375</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.04229166666666666</v>
+      </c>
+      <c r="D32" t="n">
+        <v>172.7859166666667</v>
+      </c>
+      <c r="E32" t="n">
+        <v>648.24325</v>
+      </c>
+      <c r="F32" t="n">
+        <v>269.1196666666666</v>
+      </c>
+      <c r="G32" t="n">
+        <v>369.5902916666666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>926.1660416666667</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1073.66325</v>
+      </c>
+      <c r="J32" t="n">
+        <v>45.92058333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2889,7 +3011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3248,7 +3370,7 @@
         <v>46311</v>
       </c>
       <c r="D30" t="n">
-        <v>8816.028458333334</v>
+        <v>8814.876333333332</v>
       </c>
     </row>
     <row r="31">
@@ -3256,7 +3378,7 @@
         <v>46312</v>
       </c>
       <c r="D31" t="n">
-        <v>8524.979374999997</v>
+        <v>8523.86125</v>
       </c>
     </row>
     <row r="32">
@@ -3264,7 +3386,7 @@
         <v>46313</v>
       </c>
       <c r="D32" t="n">
-        <v>10122.000375</v>
+        <v>10120.960375</v>
       </c>
     </row>
     <row r="33">
@@ -3272,7 +3394,7 @@
         <v>46314</v>
       </c>
       <c r="D33" t="n">
-        <v>11791.06633333334</v>
+        <v>11790.06625</v>
       </c>
     </row>
     <row r="34">
@@ -3280,7 +3402,7 @@
         <v>46315</v>
       </c>
       <c r="D34" t="n">
-        <v>12527.55491666667</v>
+        <v>12529.71883333333</v>
       </c>
     </row>
     <row r="35">
@@ -3294,7 +3416,7 @@
         <v>21572.77395833334</v>
       </c>
       <c r="D35" t="n">
-        <v>11261.56220833333</v>
+        <v>11259.05754166667</v>
       </c>
     </row>
     <row r="36">
@@ -3308,7 +3430,7 @@
         <v>22084.007</v>
       </c>
       <c r="D36" t="n">
-        <v>11609.65154166667</v>
+        <v>11608.27654166667</v>
       </c>
     </row>
     <row r="37">
@@ -3322,7 +3444,7 @@
         <v>22079.66070833334</v>
       </c>
       <c r="D37" t="n">
-        <v>8979.143875</v>
+        <v>8974.439208333331</v>
       </c>
     </row>
     <row r="38">
@@ -3330,13 +3452,13 @@
         <v>46319</v>
       </c>
       <c r="B38" t="n">
-        <v>19313.90845833334</v>
+        <v>19313.90779166667</v>
       </c>
       <c r="C38" t="n">
-        <v>20935.61208333333</v>
+        <v>20943.81766666667</v>
       </c>
       <c r="D38" t="n">
-        <v>7781.862416666666</v>
+        <v>7847.977333333333</v>
       </c>
     </row>
     <row r="39">
@@ -3344,13 +3466,69 @@
         <v>46320</v>
       </c>
       <c r="B39" t="n">
-        <v>18446.27329166667</v>
+        <v>18446.27304166666</v>
       </c>
       <c r="C39" t="n">
-        <v>20525.87</v>
+        <v>20532.29816666666</v>
       </c>
       <c r="D39" t="n">
-        <v>7427.636833333334</v>
+        <v>7447.874875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B40" t="n">
+        <v>19565.24074999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>22175.187375</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8043.391291666667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B41" t="n">
+        <v>20269.92466666666</v>
+      </c>
+      <c r="C41" t="n">
+        <v>22318.409875</v>
+      </c>
+      <c r="D41" t="n">
+        <v>9024.952958333333</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B42" t="n">
+        <v>20677.965625</v>
+      </c>
+      <c r="C42" t="n">
+        <v>22092.214375</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9275.87225</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B43" t="n">
+        <v>21033.70058333334</v>
+      </c>
+      <c r="C43" t="n">
+        <v>22345.88416666667</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8097.932416666667</v>
       </c>
     </row>
   </sheetData>
@@ -3364,7 +3542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3538,7 +3716,7 @@
         <v>46167</v>
       </c>
       <c r="B10" t="n">
-        <v>66.68931131118578</v>
+        <v>66.68931131118579</v>
       </c>
       <c r="C10" t="n">
         <v>12.70358187885527</v>
@@ -3748,7 +3926,7 @@
         <v>15.19215134579511</v>
       </c>
       <c r="D22" t="n">
-        <v>13.96105661434978</v>
+        <v>13.96105661434977</v>
       </c>
       <c r="E22" t="n">
         <v>0.4646170386464079</v>
@@ -3810,10 +3988,10 @@
         <v>46279</v>
       </c>
       <c r="B26" t="n">
-        <v>71.47255213310446</v>
+        <v>71.47046174578924</v>
       </c>
       <c r="C26" t="n">
-        <v>12.78394940156672</v>
+        <v>12.78603978888194</v>
       </c>
       <c r="D26" t="n">
         <v>15.73679000566285</v>
@@ -3844,13 +4022,13 @@
         <v>46293</v>
       </c>
       <c r="B28" t="n">
-        <v>70.77904214053693</v>
+        <v>70.77916195991567</v>
       </c>
       <c r="C28" t="n">
         <v>12.64205941615643</v>
       </c>
       <c r="D28" t="n">
-        <v>16.40219581607935</v>
+        <v>16.40207599670061</v>
       </c>
       <c r="E28" t="n">
         <v>0.1767026272272887</v>
@@ -3861,13 +4039,13 @@
         <v>46300</v>
       </c>
       <c r="B29" t="n">
-        <v>69.45402180196547</v>
+        <v>69.52875204245953</v>
       </c>
       <c r="C29" t="n">
         <v>13.8353926782126</v>
       </c>
       <c r="D29" t="n">
-        <v>16.52173378518143</v>
+        <v>16.44700354468735</v>
       </c>
       <c r="E29" t="n">
         <v>0.1888517346405075</v>
@@ -3878,13 +4056,13 @@
         <v>46307</v>
       </c>
       <c r="B30" t="n">
-        <v>68.83048738344954</v>
+        <v>68.91249945927666</v>
       </c>
       <c r="C30" t="n">
         <v>13.1267393226801</v>
       </c>
       <c r="D30" t="n">
-        <v>18.04277329387036</v>
+        <v>17.96076121804325</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3895,16 +4073,33 @@
         <v>46314</v>
       </c>
       <c r="B31" t="n">
-        <v>65.445539118385</v>
+        <v>65.43101831233361</v>
       </c>
       <c r="C31" t="n">
-        <v>13.50209187430443</v>
+        <v>13.50091211426762</v>
       </c>
       <c r="D31" t="n">
-        <v>21.0146773700396</v>
+        <v>21.03037793612779</v>
       </c>
       <c r="E31" t="n">
         <v>0.03769163727097908</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B32" t="n">
+        <v>70.18846136310458</v>
+      </c>
+      <c r="C32" t="n">
+        <v>12.16479680230958</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17.61677677760344</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.02996505698240977</v>
       </c>
     </row>
   </sheetData>
@@ -3918,7 +4113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4934,6 +5129,102 @@
       </c>
       <c r="J31" t="n">
         <v>69.6763202725724</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>78.23529411764706</v>
+      </c>
+      <c r="D32" t="n">
+        <v>77.84313725490196</v>
+      </c>
+      <c r="E32" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="F32" t="n">
+        <v>35.92537313432836</v>
+      </c>
+      <c r="G32" t="n">
+        <v>35.92537313432836</v>
+      </c>
+      <c r="H32" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>60.47700170357751</v>
+      </c>
+      <c r="J32" t="n">
+        <v>60.47700170357751</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>81.76470588235296</v>
+      </c>
+      <c r="D33" t="n">
+        <v>78.62745098039215</v>
+      </c>
+      <c r="E33" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.88059701492538</v>
+      </c>
+      <c r="G33" t="n">
+        <v>36.11940298507463</v>
+      </c>
+      <c r="H33" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>69.6763202725724</v>
+      </c>
+      <c r="J33" t="n">
+        <v>60.47700170357751</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83</v>
+      </c>
+      <c r="C34" t="n">
+        <v>81.37254901960785</v>
+      </c>
+      <c r="D34" t="n">
+        <v>81.37254901960785</v>
+      </c>
+      <c r="E34" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="F34" t="n">
+        <v>39.61194029850746</v>
+      </c>
+      <c r="G34" t="n">
+        <v>39.61194029850746</v>
+      </c>
+      <c r="H34" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>62.86201022146507</v>
+      </c>
+      <c r="J34" t="n">
+        <v>62.86201022146507</v>
       </c>
     </row>
   </sheetData>
@@ -4947,7 +5238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5395,6 +5686,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
